--- a/docs/database/FedProspect-Schema-Reference.xlsx
+++ b/docs/database/FedProspect-Schema-Reference.xlsx
@@ -516,7 +516,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-22</t>
+          <t>Generated: 2026-03-29</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>Total: 66 tables (59 production + 7 staging) + 12 views</t>
+          <t>Total: 70 tables (63 production + 7 staging) + 12 views</t>
         </is>
       </c>
     </row>
@@ -698,10 +698,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G157"/>
+  <dimension ref="A1:G102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
@@ -1420,12 +1420,12 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>estimated_contract_value</t>
+          <t>pricing_structure</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>DECIMAL(15</t>
+          <t>VARCHAR(50)</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -1445,12 +1445,12 @@
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>place_of_performance_detail</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>CHAR(1)</t>
+          <t>VARCHAR(200)</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
@@ -1458,32 +1458,24 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D29" s="6" t="inlineStr"/>
       <c r="E29" s="6" t="inlineStr"/>
-      <c r="F29" s="6" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="F29" s="6" t="inlineStr"/>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>Y/N whether opportunity is active</t>
+          <t>Reserved: not in public Opportunities API v2 response</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>award_number</t>
+          <t>estimated_contract_value</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>VARCHAR(200)</t>
+          <t>DECIMAL(15</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -1496,19 +1488,19 @@
       <c r="F30" s="5" t="inlineStr"/>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>Contract award number if awarded</t>
+          <t>Reserved: not in public Opportunities API v2 response</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>award_date</t>
+          <t>active</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>DATE</t>
+          <t>CHAR(1)</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
@@ -1516,24 +1508,32 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr"/>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E31" s="6" t="inlineStr"/>
-      <c r="F31" s="6" t="inlineStr"/>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>Date contract was awarded</t>
+          <t>Y/N whether opportunity is active</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>award_amount</t>
+          <t>award_number</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>DECIMAL(15</t>
+          <t>VARCHAR(200)</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
@@ -1546,19 +1546,19 @@
       <c r="F32" s="5" t="inlineStr"/>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Dollar amount of award</t>
+          <t>Contract award number if awarded</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>awardee_uei</t>
+          <t>award_date</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>VARCHAR(12)</t>
+          <t>DATE</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
@@ -1571,19 +1571,19 @@
       <c r="F33" s="6" t="inlineStr"/>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>UEI of winning contractor</t>
+          <t>Date contract was awarded</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>awardee_name</t>
+          <t>award_amount</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>VARCHAR(200)</t>
+          <t>DECIMAL(15</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -1596,19 +1596,19 @@
       <c r="F34" s="5" t="inlineStr"/>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>Name of winning contractor</t>
+          <t>Dollar amount of award</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>awardee_cage_code</t>
+          <t>awardee_uei</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>VARCHAR(10)</t>
+          <t>VARCHAR(12)</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
@@ -1621,19 +1621,19 @@
       <c r="F35" s="6" t="inlineStr"/>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>CAGE code of winning contractor</t>
+          <t>UEI of winning contractor</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>awardee_city</t>
+          <t>awardee_name</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>VARCHAR(100)</t>
+          <t>VARCHAR(200)</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
@@ -1644,17 +1644,21 @@
       <c r="D36" s="5" t="inlineStr"/>
       <c r="E36" s="5" t="inlineStr"/>
       <c r="F36" s="5" t="inlineStr"/>
-      <c r="G36" s="5" t="inlineStr"/>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>Name of winning contractor</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>awardee_state</t>
+          <t>awardee_cage_code</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>VARCHAR(50)</t>
+          <t>VARCHAR(10)</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
@@ -1665,17 +1669,21 @@
       <c r="D37" s="6" t="inlineStr"/>
       <c r="E37" s="6" t="inlineStr"/>
       <c r="F37" s="6" t="inlineStr"/>
-      <c r="G37" s="6" t="inlineStr"/>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>CAGE code of winning contractor</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>awardee_zip</t>
+          <t>awardee_city</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>VARCHAR(100)</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
@@ -1686,21 +1694,17 @@
       <c r="D38" s="5" t="inlineStr"/>
       <c r="E38" s="5" t="inlineStr"/>
       <c r="F38" s="5" t="inlineStr"/>
-      <c r="G38" s="5" t="inlineStr">
-        <is>
-          <t>Military APO/FPO zips can be 17+ chars</t>
-        </is>
-      </c>
+      <c r="G38" s="5" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>full_parent_path_name</t>
+          <t>awardee_state</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>VARCHAR(500)</t>
+          <t>VARCHAR(50)</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
@@ -1711,21 +1715,17 @@
       <c r="D39" s="6" t="inlineStr"/>
       <c r="E39" s="6" t="inlineStr"/>
       <c r="F39" s="6" t="inlineStr"/>
-      <c r="G39" s="6" t="inlineStr">
-        <is>
-          <t>Full agency hierarchy path (names)</t>
-        </is>
-      </c>
+      <c r="G39" s="6" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>full_parent_path_code</t>
+          <t>awardee_zip</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>VARCHAR(200)</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
@@ -1738,14 +1738,14 @@
       <c r="F40" s="5" t="inlineStr"/>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>Full agency hierarchy path (codes)</t>
+          <t>Military APO/FPO zips can be 17+ chars</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>description_url</t>
+          <t>full_parent_path_name</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
@@ -1763,19 +1763,19 @@
       <c r="F41" s="6" t="inlineStr"/>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>URL to fetch description via SAM.gov API</t>
+          <t>Full agency hierarchy path (names)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>description_text</t>
+          <t>full_parent_path_code</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>LONGTEXT</t>
+          <t>VARCHAR(200)</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
@@ -1788,14 +1788,14 @@
       <c r="F42" s="5" t="inlineStr"/>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>Cached description fetched from description_url</t>
+          <t>Full agency hierarchy path (codes)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>link</t>
+          <t>description_url</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
@@ -1813,19 +1813,19 @@
       <c r="F43" s="6" t="inlineStr"/>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>Direct link to opportunity on SAM.gov</t>
+          <t>URL to fetch description via SAM.gov API</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>resource_links</t>
+          <t>description_text</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>JSON</t>
+          <t>LONGTEXT</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
@@ -1838,19 +1838,19 @@
       <c r="F44" s="5" t="inlineStr"/>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>JSON array of additional resource URLs</t>
+          <t>Cached description fetched from description_url</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>contracting_office_id</t>
+          <t>link</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>VARCHAR(500)</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
@@ -1863,19 +1863,19 @@
       <c r="F45" s="6" t="inlineStr"/>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>Contracting office identifier</t>
+          <t>Direct link to opportunity on SAM.gov</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>record_hash</t>
+          <t>resource_links</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>CHAR(64)</t>
+          <t>JSON</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
@@ -1888,19 +1888,19 @@
       <c r="F46" s="5" t="inlineStr"/>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>SHA-256 hash for change detection</t>
+          <t>JSON array of additional resource URLs</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>first_loaded_at</t>
+          <t>contracting_office_id</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>DATETIME</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
@@ -1908,28 +1908,24 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
-          <t>CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
+      <c r="D47" s="6" t="inlineStr"/>
       <c r="E47" s="6" t="inlineStr"/>
       <c r="F47" s="6" t="inlineStr"/>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>Timestamp of initial ETL load</t>
+          <t>Contracting office identifier</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>last_loaded_at</t>
+          <t>record_hash</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>DATETIME</t>
+          <t>CHAR(64)</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
@@ -1937,28 +1933,24 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="D48" s="5" t="inlineStr">
-        <is>
-          <t>CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
+      <c r="D48" s="5" t="inlineStr"/>
       <c r="E48" s="5" t="inlineStr"/>
       <c r="F48" s="5" t="inlineStr"/>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>Timestamp of most recent ETL load</t>
+          <t>SHA-256 hash for change detection</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>last_load_id</t>
+          <t>first_loaded_at</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>INT</t>
+          <t>DATETIME</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
@@ -1966,188 +1958,196 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="D49" s="6" t="inlineStr"/>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
       <c r="E49" s="6" t="inlineStr"/>
       <c r="F49" s="6" t="inlineStr"/>
       <c r="G49" s="6" t="inlineStr">
         <is>
+          <t>Timestamp of initial ETL load</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>last_loaded_at</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>DATETIME</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr"/>
+      <c r="F50" s="5" t="inlineStr"/>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>Timestamp of most recent ETL load</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>last_load_id</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr"/>
+      <c r="E51" s="6" t="inlineStr"/>
+      <c r="F51" s="6" t="inlineStr"/>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
           <t>FK to etl_load_log for traceability</t>
         </is>
       </c>
     </row>
-    <row r="50"/>
-    <row r="51">
-      <c r="A51" s="8" t="inlineStr">
+    <row r="52"/>
+    <row r="53">
+      <c r="A53" s="8" t="inlineStr">
         <is>
           <t>opportunity_history</t>
         </is>
       </c>
-      <c r="B51" s="9" t="n"/>
-      <c r="C51" s="9" t="n"/>
-      <c r="D51" s="9" t="n"/>
-      <c r="E51" s="9" t="n"/>
-      <c r="F51" s="9" t="n"/>
-      <c r="G51" s="9" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="10" t="inlineStr">
+      <c r="B53" s="9" t="n"/>
+      <c r="C53" s="9" t="n"/>
+      <c r="D53" s="9" t="n"/>
+      <c r="E53" s="9" t="n"/>
+      <c r="F53" s="9" t="n"/>
+      <c r="G53" s="9" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="10" t="inlineStr">
         <is>
           <t>Column Name</t>
         </is>
       </c>
-      <c r="B52" s="10" t="inlineStr">
+      <c r="B54" s="10" t="inlineStr">
         <is>
           <t>Data Type</t>
         </is>
       </c>
-      <c r="C52" s="10" t="inlineStr">
+      <c r="C54" s="10" t="inlineStr">
         <is>
           <t>Nullable</t>
         </is>
       </c>
-      <c r="D52" s="10" t="inlineStr">
+      <c r="D54" s="10" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="E52" s="10" t="inlineStr">
+      <c r="E54" s="10" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="F52" s="10" t="inlineStr">
+      <c r="F54" s="10" t="inlineStr">
         <is>
           <t>Index</t>
         </is>
       </c>
-      <c r="G52" s="10" t="inlineStr">
+      <c r="G54" s="10" t="inlineStr">
         <is>
           <t>Description</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B53" s="6" t="inlineStr">
-        <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="inlineStr"/>
-      <c r="E53" s="6" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="F53" s="6" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G53" s="6" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>notice_id</t>
-        </is>
-      </c>
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>VARCHAR(100)</t>
-        </is>
-      </c>
-      <c r="C54" s="5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="inlineStr"/>
-      <c r="E54" s="5" t="inlineStr"/>
-      <c r="F54" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G54" s="5" t="inlineStr">
-        <is>
-          <t>SAM.gov opportunity identifier</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>field_name</t>
+          <t>id</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>VARCHAR(100)</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr"/>
-      <c r="E55" s="6" t="inlineStr"/>
-      <c r="F55" s="6" t="inlineStr"/>
-      <c r="G55" s="6" t="inlineStr">
-        <is>
-          <t>Changed field name</t>
-        </is>
-      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>old_value</t>
+          <t>notice_id</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>VARCHAR(100)</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr"/>
       <c r="E56" s="5" t="inlineStr"/>
-      <c r="F56" s="5" t="inlineStr"/>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>Previous field value</t>
+          <t>SAM.gov opportunity identifier</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>new_value</t>
+          <t>field_name</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>VARCHAR(100)</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr"/>
@@ -2155,19 +2155,19 @@
       <c r="F57" s="6" t="inlineStr"/>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>New field value</t>
+          <t>Changed field name</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>changed_at</t>
+          <t>old_value</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>DATETIME</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
@@ -2175,37 +2175,29 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="D58" s="5" t="inlineStr">
-        <is>
-          <t>CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
+      <c r="D58" s="5" t="inlineStr"/>
       <c r="E58" s="5" t="inlineStr"/>
-      <c r="F58" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="F58" s="5" t="inlineStr"/>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>When change was detected</t>
+          <t>Previous field value</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>load_id</t>
+          <t>new_value</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>INT</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr"/>
@@ -2213,157 +2205,157 @@
       <c r="F59" s="6" t="inlineStr"/>
       <c r="G59" s="6" t="inlineStr">
         <is>
+          <t>New field value</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>changed_at</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>DATETIME</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="inlineStr"/>
+      <c r="F60" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G60" s="5" t="inlineStr">
+        <is>
+          <t>When change was detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>load_id</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr"/>
+      <c r="E61" s="6" t="inlineStr"/>
+      <c r="F61" s="6" t="inlineStr"/>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
           <t>FK to etl_load_log</t>
         </is>
       </c>
     </row>
-    <row r="60"/>
-    <row r="61">
-      <c r="A61" s="8" t="inlineStr">
+    <row r="62"/>
+    <row r="63">
+      <c r="A63" s="8" t="inlineStr">
         <is>
           <t>opportunity_relationship</t>
         </is>
       </c>
-      <c r="B61" s="9" t="n"/>
-      <c r="C61" s="9" t="n"/>
-      <c r="D61" s="9" t="n"/>
-      <c r="E61" s="9" t="n"/>
-      <c r="F61" s="9" t="n"/>
-      <c r="G61" s="9" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="10" t="inlineStr">
+      <c r="B63" s="9" t="n"/>
+      <c r="C63" s="9" t="n"/>
+      <c r="D63" s="9" t="n"/>
+      <c r="E63" s="9" t="n"/>
+      <c r="F63" s="9" t="n"/>
+      <c r="G63" s="9" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="10" t="inlineStr">
         <is>
           <t>Column Name</t>
         </is>
       </c>
-      <c r="B62" s="10" t="inlineStr">
+      <c r="B64" s="10" t="inlineStr">
         <is>
           <t>Data Type</t>
         </is>
       </c>
-      <c r="C62" s="10" t="inlineStr">
+      <c r="C64" s="10" t="inlineStr">
         <is>
           <t>Nullable</t>
         </is>
       </c>
-      <c r="D62" s="10" t="inlineStr">
+      <c r="D64" s="10" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="E62" s="10" t="inlineStr">
+      <c r="E64" s="10" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="F62" s="10" t="inlineStr">
+      <c r="F64" s="10" t="inlineStr">
         <is>
           <t>Index</t>
         </is>
       </c>
-      <c r="G62" s="10" t="inlineStr">
+      <c r="G64" s="10" t="inlineStr">
         <is>
           <t>Description</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="6" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B63" s="6" t="inlineStr">
-        <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="C63" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D63" s="6" t="inlineStr"/>
-      <c r="E63" s="6" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="F63" s="6" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G63" s="6" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>parent_notice_id</t>
-        </is>
-      </c>
-      <c r="B64" s="5" t="inlineStr">
-        <is>
-          <t>VARCHAR(100)</t>
-        </is>
-      </c>
-      <c r="C64" s="5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D64" s="5" t="inlineStr"/>
-      <c r="E64" s="5" t="inlineStr"/>
-      <c r="F64" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G64" s="5" t="inlineStr">
-        <is>
-          <t>Parent opportunity notice_id</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>child_notice_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>VARCHAR(100)</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr"/>
-      <c r="E65" s="6" t="inlineStr"/>
+      <c r="E65" s="6" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="F65" s="6" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="G65" s="6" t="inlineStr">
-        <is>
-          <t>Child opportunity notice_id</t>
-        </is>
-      </c>
+      <c r="G65" s="6" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>relationship_type</t>
+          <t>parent_notice_id</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>VARCHAR(30)</t>
+          <t>VARCHAR(100)</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
@@ -2373,76 +2365,80 @@
       </c>
       <c r="D66" s="5" t="inlineStr"/>
       <c r="E66" s="5" t="inlineStr"/>
-      <c r="F66" s="5" t="inlineStr"/>
+      <c r="F66" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>Relationship type (RFI_TO_RFP, etc.)</t>
+          <t>Parent opportunity notice_id</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>created_by</t>
+          <t>child_notice_id</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>INT</t>
+          <t>VARCHAR(100)</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr"/>
       <c r="E67" s="6" t="inlineStr"/>
-      <c r="F67" s="6" t="inlineStr"/>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>User who created the relationship</t>
+          <t>Child opportunity notice_id</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>relationship_type</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>DATETIME</t>
+          <t>VARCHAR(30)</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D68" s="5" t="inlineStr">
-        <is>
-          <t>CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr"/>
       <c r="E68" s="5" t="inlineStr"/>
       <c r="F68" s="5" t="inlineStr"/>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>Row creation timestamp</t>
+          <t>Relationship type (RFI_TO_RFP, etc.)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>created_by</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
@@ -2455,132 +2451,124 @@
       <c r="F69" s="6" t="inlineStr"/>
       <c r="G69" s="6" t="inlineStr">
         <is>
+          <t>User who created the relationship</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>DATETIME</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="inlineStr"/>
+      <c r="F70" s="5" t="inlineStr"/>
+      <c r="G70" s="5" t="inlineStr">
+        <is>
+          <t>Row creation timestamp</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr"/>
+      <c r="E71" s="6" t="inlineStr"/>
+      <c r="F71" s="6" t="inlineStr"/>
+      <c r="G71" s="6" t="inlineStr">
+        <is>
           <t>Additional notes</t>
         </is>
       </c>
     </row>
-    <row r="70"/>
-    <row r="71">
-      <c r="A71" s="8" t="inlineStr">
+    <row r="72"/>
+    <row r="73">
+      <c r="A73" s="8" t="inlineStr">
         <is>
           <t>opportunity_attachment</t>
         </is>
       </c>
-      <c r="B71" s="9" t="n"/>
-      <c r="C71" s="9" t="n"/>
-      <c r="D71" s="9" t="n"/>
-      <c r="E71" s="9" t="n"/>
-      <c r="F71" s="9" t="n"/>
-      <c r="G71" s="9" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="10" t="inlineStr">
+      <c r="B73" s="9" t="n"/>
+      <c r="C73" s="9" t="n"/>
+      <c r="D73" s="9" t="n"/>
+      <c r="E73" s="9" t="n"/>
+      <c r="F73" s="9" t="n"/>
+      <c r="G73" s="9" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="10" t="inlineStr">
         <is>
           <t>Column Name</t>
         </is>
       </c>
-      <c r="B72" s="10" t="inlineStr">
+      <c r="B74" s="10" t="inlineStr">
         <is>
           <t>Data Type</t>
         </is>
       </c>
-      <c r="C72" s="10" t="inlineStr">
+      <c r="C74" s="10" t="inlineStr">
         <is>
           <t>Nullable</t>
         </is>
       </c>
-      <c r="D72" s="10" t="inlineStr">
+      <c r="D74" s="10" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="E72" s="10" t="inlineStr">
+      <c r="E74" s="10" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="F72" s="10" t="inlineStr">
+      <c r="F74" s="10" t="inlineStr">
         <is>
           <t>Index</t>
         </is>
       </c>
-      <c r="G72" s="10" t="inlineStr">
+      <c r="G74" s="10" t="inlineStr">
         <is>
           <t>Description</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="6" t="inlineStr">
-        <is>
-          <t>attachment_id</t>
-        </is>
-      </c>
-      <c r="B73" s="6" t="inlineStr">
-        <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="C73" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D73" s="6" t="inlineStr"/>
-      <c r="E73" s="6" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="F73" s="6" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G73" s="6" t="inlineStr">
-        <is>
-          <t>Auto-increment attachment identifier</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="5" t="inlineStr">
-        <is>
-          <t>notice_id</t>
-        </is>
-      </c>
-      <c r="B74" s="5" t="inlineStr">
-        <is>
-          <t>VARCHAR(100)</t>
-        </is>
-      </c>
-      <c r="C74" s="5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D74" s="5" t="inlineStr"/>
-      <c r="E74" s="5" t="inlineStr"/>
-      <c r="F74" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G74" s="5" t="inlineStr">
-        <is>
-          <t>SAM.gov opportunity identifier</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>url</t>
+          <t>notice_id</t>
         </is>
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>VARCHAR(500)</t>
+          <t>VARCHAR(100)</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
@@ -2589,7 +2577,11 @@
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr"/>
-      <c r="E75" s="6" t="inlineStr"/>
+      <c r="E75" s="6" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="F75" s="6" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2597,49 +2589,57 @@
       </c>
       <c r="G75" s="6" t="inlineStr">
         <is>
-          <t>Download URL for the attachment</t>
+          <t>SAM.gov opportunity identifier</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>filename</t>
+          <t>attachment_id</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>VARCHAR(500)</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr"/>
-      <c r="E76" s="5" t="inlineStr"/>
-      <c r="F76" s="5" t="inlineStr"/>
+      <c r="E76" s="5" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="F76" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
-          <t>Original filename of attachment</t>
+          <t>Auto-increment attachment identifier</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>content_type</t>
+          <t>url</t>
         </is>
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>VARCHAR(100)</t>
+          <t>VARCHAR(500)</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr"/>
@@ -2647,19 +2647,19 @@
       <c r="F77" s="6" t="inlineStr"/>
       <c r="G77" s="6" t="inlineStr">
         <is>
-          <t>MIME type of file content</t>
+          <t>Download URL for the attachment</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>file_size_bytes</t>
+          <t>last_load_id</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
@@ -2672,19 +2672,19 @@
       <c r="F78" s="5" t="inlineStr"/>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>File size in bytes</t>
+          <t>FK to etl_load_log for traceability</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>file_path</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>VARCHAR(500)</t>
+          <t>DATETIME</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
@@ -2692,103 +2692,79 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="D79" s="6" t="inlineStr"/>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
       <c r="E79" s="6" t="inlineStr"/>
       <c r="F79" s="6" t="inlineStr"/>
       <c r="G79" s="6" t="inlineStr">
         <is>
-          <t>Local filesystem path to downloaded file</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="5" t="inlineStr">
-        <is>
-          <t>extracted_text</t>
-        </is>
-      </c>
-      <c r="B80" s="5" t="inlineStr">
-        <is>
-          <t>LONGTEXT</t>
-        </is>
-      </c>
-      <c r="C80" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D80" s="5" t="inlineStr"/>
-      <c r="E80" s="5" t="inlineStr"/>
-      <c r="F80" s="5" t="inlineStr"/>
-      <c r="G80" s="5" t="inlineStr">
-        <is>
-          <t>Full text extracted from document</t>
-        </is>
-      </c>
-    </row>
+          <t>Row creation timestamp</t>
+        </is>
+      </c>
+    </row>
+    <row r="80"/>
     <row r="81">
-      <c r="A81" s="6" t="inlineStr">
-        <is>
-          <t>page_count</t>
-        </is>
-      </c>
-      <c r="B81" s="6" t="inlineStr">
-        <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="C81" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D81" s="6" t="inlineStr"/>
-      <c r="E81" s="6" t="inlineStr"/>
-      <c r="F81" s="6" t="inlineStr"/>
-      <c r="G81" s="6" t="inlineStr">
-        <is>
-          <t>Number of pages in document</t>
-        </is>
-      </c>
+      <c r="A81" s="8" t="inlineStr">
+        <is>
+          <t>opportunity_poc</t>
+        </is>
+      </c>
+      <c r="B81" s="9" t="n"/>
+      <c r="C81" s="9" t="n"/>
+      <c r="D81" s="9" t="n"/>
+      <c r="E81" s="9" t="n"/>
+      <c r="F81" s="9" t="n"/>
+      <c r="G81" s="9" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t>is_scanned</t>
-        </is>
-      </c>
-      <c r="B82" s="5" t="inlineStr">
-        <is>
-          <t>TINYINT</t>
-        </is>
-      </c>
-      <c r="C82" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D82" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E82" s="5" t="inlineStr"/>
-      <c r="F82" s="5" t="inlineStr"/>
-      <c r="G82" s="5" t="inlineStr">
-        <is>
-          <t>Whether document is a scanned image (OCR needed)</t>
+      <c r="A82" s="10" t="inlineStr">
+        <is>
+          <t>Column Name</t>
+        </is>
+      </c>
+      <c r="B82" s="10" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="C82" s="10" t="inlineStr">
+        <is>
+          <t>Nullable</t>
+        </is>
+      </c>
+      <c r="D82" s="10" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="E82" s="10" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="F82" s="10" t="inlineStr">
+        <is>
+          <t>Index</t>
+        </is>
+      </c>
+      <c r="G82" s="10" t="inlineStr">
+        <is>
+          <t>Description</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>ocr_quality</t>
+          <t>poc_id</t>
         </is>
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>ENUM(</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
@@ -2797,35 +2773,39 @@
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr"/>
-      <c r="E83" s="6" t="inlineStr"/>
-      <c r="F83" s="6" t="inlineStr"/>
+      <c r="E83" s="6" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="F83" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="G83" s="6" t="inlineStr">
         <is>
-          <t>Quality of OCR extraction (good/fair/poor)</t>
+          <t>Auto-increment POC identifier</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>download_status</t>
+          <t>notice_id</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>ENUM(</t>
+          <t>VARCHAR(100)</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D84" s="5" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D84" s="5" t="inlineStr"/>
       <c r="E84" s="5" t="inlineStr"/>
       <c r="F84" s="5" t="inlineStr">
         <is>
@@ -2834,31 +2814,27 @@
       </c>
       <c r="G84" s="5" t="inlineStr">
         <is>
-          <t>File download state machine status</t>
+          <t>SAM.gov opportunity identifier</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>extraction_status</t>
+          <t>officer_id</t>
         </is>
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>ENUM(</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D85" s="6" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr"/>
       <c r="E85" s="6" t="inlineStr"/>
       <c r="F85" s="6" t="inlineStr">
         <is>
@@ -2867,44 +2843,52 @@
       </c>
       <c r="G85" s="6" t="inlineStr">
         <is>
-          <t>Text extraction state machine status</t>
+          <t>FK to contracting_officer</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>content_hash</t>
+          <t>poc_type</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>CHAR(64)</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D86" s="5" t="inlineStr"/>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D86" s="5" t="inlineStr">
+        <is>
+          <t>PRIMARY</t>
+        </is>
+      </c>
       <c r="E86" s="5" t="inlineStr"/>
-      <c r="F86" s="5" t="inlineStr"/>
+      <c r="F86" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="G86" s="5" t="inlineStr">
         <is>
-          <t>SHA-256 hash of file content</t>
+          <t>Contact type (PRIMARY, SECONDARY)</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>text_hash</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>CHAR(64)</t>
+          <t>DATETIME</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
@@ -2912,99 +2896,79 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="D87" s="6" t="inlineStr"/>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
       <c r="E87" s="6" t="inlineStr"/>
       <c r="F87" s="6" t="inlineStr"/>
       <c r="G87" s="6" t="inlineStr">
         <is>
-          <t>SHA-256 hash of extracted text</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="5" t="inlineStr">
-        <is>
-          <t>downloaded_at</t>
-        </is>
-      </c>
-      <c r="B88" s="5" t="inlineStr">
-        <is>
-          <t>DATETIME</t>
-        </is>
-      </c>
-      <c r="C88" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D88" s="5" t="inlineStr"/>
-      <c r="E88" s="5" t="inlineStr"/>
-      <c r="F88" s="5" t="inlineStr"/>
-      <c r="G88" s="5" t="inlineStr">
-        <is>
-          <t>When file was downloaded</t>
-        </is>
-      </c>
-    </row>
+          <t>Row creation timestamp</t>
+        </is>
+      </c>
+    </row>
+    <row r="88"/>
     <row r="89">
-      <c r="A89" s="6" t="inlineStr">
-        <is>
-          <t>extracted_at</t>
-        </is>
-      </c>
-      <c r="B89" s="6" t="inlineStr">
-        <is>
-          <t>DATETIME</t>
-        </is>
-      </c>
-      <c r="C89" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D89" s="6" t="inlineStr"/>
-      <c r="E89" s="6" t="inlineStr"/>
-      <c r="F89" s="6" t="inlineStr"/>
-      <c r="G89" s="6" t="inlineStr">
-        <is>
-          <t>When text was extracted</t>
-        </is>
-      </c>
+      <c r="A89" s="8" t="inlineStr">
+        <is>
+          <t>contracting_officer</t>
+        </is>
+      </c>
+      <c r="B89" s="9" t="n"/>
+      <c r="C89" s="9" t="n"/>
+      <c r="D89" s="9" t="n"/>
+      <c r="E89" s="9" t="n"/>
+      <c r="F89" s="9" t="n"/>
+      <c r="G89" s="9" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" s="5" t="inlineStr">
-        <is>
-          <t>last_load_id</t>
-        </is>
-      </c>
-      <c r="B90" s="5" t="inlineStr">
-        <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="C90" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D90" s="5" t="inlineStr"/>
-      <c r="E90" s="5" t="inlineStr"/>
-      <c r="F90" s="5" t="inlineStr"/>
-      <c r="G90" s="5" t="inlineStr">
-        <is>
-          <t>FK to etl_load_log for traceability</t>
+      <c r="A90" s="10" t="inlineStr">
+        <is>
+          <t>Column Name</t>
+        </is>
+      </c>
+      <c r="B90" s="10" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="C90" s="10" t="inlineStr">
+        <is>
+          <t>Nullable</t>
+        </is>
+      </c>
+      <c r="D90" s="10" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="E90" s="10" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="F90" s="10" t="inlineStr">
+        <is>
+          <t>Index</t>
+        </is>
+      </c>
+      <c r="G90" s="10" t="inlineStr">
+        <is>
+          <t>Description</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>officer_id</t>
         </is>
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>DATETIME</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
@@ -3012,79 +2976,111 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="D91" s="6" t="inlineStr">
-        <is>
-          <t>CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="E91" s="6" t="inlineStr"/>
-      <c r="F91" s="6" t="inlineStr"/>
+      <c r="D91" s="6" t="inlineStr"/>
+      <c r="E91" s="6" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="F91" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="G91" s="6" t="inlineStr">
         <is>
-          <t>Row creation timestamp</t>
-        </is>
-      </c>
-    </row>
-    <row r="92"/>
+          <t>FK to contracting_officer</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>full_name</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>VARCHAR(500)</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="inlineStr"/>
+      <c r="E92" s="5" t="inlineStr"/>
+      <c r="F92" s="5" t="inlineStr"/>
+      <c r="G92" s="5" t="inlineStr">
+        <is>
+          <t>Officer full name</t>
+        </is>
+      </c>
+    </row>
     <row r="93">
-      <c r="A93" s="8" t="inlineStr">
-        <is>
-          <t>opportunity_attachment_intel</t>
-        </is>
-      </c>
-      <c r="B93" s="9" t="n"/>
-      <c r="C93" s="9" t="n"/>
-      <c r="D93" s="9" t="n"/>
-      <c r="E93" s="9" t="n"/>
-      <c r="F93" s="9" t="n"/>
-      <c r="G93" s="9" t="n"/>
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>VARCHAR(200)</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D93" s="6" t="inlineStr"/>
+      <c r="E93" s="6" t="inlineStr"/>
+      <c r="F93" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G93" s="6" t="inlineStr">
+        <is>
+          <t>User email address</t>
+        </is>
+      </c>
     </row>
     <row r="94">
-      <c r="A94" s="10" t="inlineStr">
-        <is>
-          <t>Column Name</t>
-        </is>
-      </c>
-      <c r="B94" s="10" t="inlineStr">
-        <is>
-          <t>Data Type</t>
-        </is>
-      </c>
-      <c r="C94" s="10" t="inlineStr">
-        <is>
-          <t>Nullable</t>
-        </is>
-      </c>
-      <c r="D94" s="10" t="inlineStr">
-        <is>
-          <t>Default</t>
-        </is>
-      </c>
-      <c r="E94" s="10" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="F94" s="10" t="inlineStr">
-        <is>
-          <t>Index</t>
-        </is>
-      </c>
-      <c r="G94" s="10" t="inlineStr">
-        <is>
-          <t>Description</t>
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="inlineStr">
+        <is>
+          <t>VARCHAR(100)</t>
+        </is>
+      </c>
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D94" s="5" t="inlineStr"/>
+      <c r="E94" s="5" t="inlineStr"/>
+      <c r="F94" s="5" t="inlineStr"/>
+      <c r="G94" s="5" t="inlineStr">
+        <is>
+          <t>Contact phone number</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>intel_id</t>
+          <t>fax</t>
         </is>
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>INT</t>
+          <t>VARCHAR(100)</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
@@ -3093,60 +3089,48 @@
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr"/>
-      <c r="E95" s="6" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="F95" s="6" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="E95" s="6" t="inlineStr"/>
+      <c r="F95" s="6" t="inlineStr"/>
       <c r="G95" s="6" t="inlineStr">
         <is>
-          <t>Auto-increment intel record identifier</t>
+          <t>Fax number</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>notice_id</t>
+          <t>title</t>
         </is>
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>VARCHAR(100)</t>
+          <t>VARCHAR(200)</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr"/>
       <c r="E96" s="5" t="inlineStr"/>
-      <c r="F96" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="F96" s="5" t="inlineStr"/>
       <c r="G96" s="5" t="inlineStr">
         <is>
-          <t>SAM.gov opportunity identifier</t>
+          <t>Opportunity title</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="6" t="inlineStr">
         <is>
-          <t>attachment_id</t>
+          <t>department_name</t>
         </is>
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>INT</t>
+          <t>VARCHAR(200)</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
@@ -3156,55 +3140,43 @@
       </c>
       <c r="D97" s="6" t="inlineStr"/>
       <c r="E97" s="6" t="inlineStr"/>
-      <c r="F97" s="6" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="F97" s="6" t="inlineStr"/>
       <c r="G97" s="6" t="inlineStr">
         <is>
-          <t>Auto-increment attachment identifier</t>
+          <t>Issuing federal department</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>extraction_method</t>
+          <t>office_name</t>
         </is>
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>ENUM(</t>
+          <t>VARCHAR(200)</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr"/>
       <c r="E98" s="5" t="inlineStr"/>
-      <c r="F98" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G98" s="5" t="inlineStr">
-        <is>
-          <t>How intel was extracted (keyword/heuristic/AI)</t>
-        </is>
-      </c>
+      <c r="F98" s="5" t="inlineStr"/>
+      <c r="G98" s="5" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="6" t="inlineStr">
         <is>
-          <t>source_text_hash</t>
+          <t>officer_type</t>
         </is>
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>CHAR(64)</t>
+          <t>VARCHAR(50)</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
@@ -3217,19 +3189,19 @@
       <c r="F99" s="6" t="inlineStr"/>
       <c r="G99" s="6" t="inlineStr">
         <is>
-          <t>Hash of source text used for extraction</t>
+          <t>Type (Contracting Officer, Specialist, etc.)</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>clearance_required</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>CHAR(1)</t>
+          <t>DATETIME</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
@@ -3237,28 +3209,28 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="D100" s="5" t="inlineStr"/>
+      <c r="D100" s="5" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
       <c r="E100" s="5" t="inlineStr"/>
-      <c r="F100" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="F100" s="5" t="inlineStr"/>
       <c r="G100" s="5" t="inlineStr">
         <is>
-          <t>Y/N security clearance needed</t>
+          <t>Row creation timestamp</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="6" t="inlineStr">
         <is>
-          <t>clearance_level</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>VARCHAR(50)</t>
+          <t>DATETIME</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
@@ -3266,1417 +3238,28 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="D101" s="6" t="inlineStr"/>
+      <c r="D101" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
       <c r="E101" s="6" t="inlineStr"/>
-      <c r="F101" s="6" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="F101" s="6" t="inlineStr"/>
       <c r="G101" s="6" t="inlineStr">
         <is>
-          <t>Required clearance level (Secret, TS, etc.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="5" t="inlineStr">
-        <is>
-          <t>clearance_scope</t>
-        </is>
-      </c>
-      <c r="B102" s="5" t="inlineStr">
-        <is>
-          <t>VARCHAR(50)</t>
-        </is>
-      </c>
-      <c r="C102" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D102" s="5" t="inlineStr"/>
-      <c r="E102" s="5" t="inlineStr"/>
-      <c r="F102" s="5" t="inlineStr"/>
-      <c r="G102" s="5" t="inlineStr">
-        <is>
-          <t>Scope of clearance requirement</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="6" t="inlineStr">
-        <is>
-          <t>clearance_details</t>
-        </is>
-      </c>
-      <c r="B103" s="6" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="C103" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D103" s="6" t="inlineStr"/>
-      <c r="E103" s="6" t="inlineStr"/>
-      <c r="F103" s="6" t="inlineStr"/>
-      <c r="G103" s="6" t="inlineStr">
-        <is>
-          <t>Free-text clearance details</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="5" t="inlineStr">
-        <is>
-          <t>eval_method</t>
-        </is>
-      </c>
-      <c r="B104" s="5" t="inlineStr">
-        <is>
-          <t>VARCHAR(50)</t>
-        </is>
-      </c>
-      <c r="C104" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D104" s="5" t="inlineStr"/>
-      <c r="E104" s="5" t="inlineStr"/>
-      <c r="F104" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G104" s="5" t="inlineStr">
-        <is>
-          <t>Evaluation methodology (LPTA, best value, etc.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="6" t="inlineStr">
-        <is>
-          <t>eval_details</t>
-        </is>
-      </c>
-      <c r="B105" s="6" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="C105" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D105" s="6" t="inlineStr"/>
-      <c r="E105" s="6" t="inlineStr"/>
-      <c r="F105" s="6" t="inlineStr"/>
-      <c r="G105" s="6" t="inlineStr">
-        <is>
-          <t>Evaluation criteria details</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="5" t="inlineStr">
-        <is>
-          <t>vehicle_type</t>
-        </is>
-      </c>
-      <c r="B106" s="5" t="inlineStr">
-        <is>
-          <t>VARCHAR(100)</t>
-        </is>
-      </c>
-      <c r="C106" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D106" s="5" t="inlineStr"/>
-      <c r="E106" s="5" t="inlineStr"/>
-      <c r="F106" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G106" s="5" t="inlineStr">
-        <is>
-          <t>Contract vehicle type (GSA, BPA, IDIQ, etc.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="6" t="inlineStr">
-        <is>
-          <t>vehicle_details</t>
-        </is>
-      </c>
-      <c r="B107" s="6" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="C107" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D107" s="6" t="inlineStr"/>
-      <c r="E107" s="6" t="inlineStr"/>
-      <c r="F107" s="6" t="inlineStr"/>
-      <c r="G107" s="6" t="inlineStr">
-        <is>
-          <t>Contract vehicle details</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="5" t="inlineStr">
-        <is>
-          <t>is_recompete</t>
-        </is>
-      </c>
-      <c r="B108" s="5" t="inlineStr">
-        <is>
-          <t>CHAR(1)</t>
-        </is>
-      </c>
-      <c r="C108" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D108" s="5" t="inlineStr"/>
-      <c r="E108" s="5" t="inlineStr"/>
-      <c r="F108" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G108" s="5" t="inlineStr">
-        <is>
-          <t>Y/N whether this is a recompete</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="6" t="inlineStr">
-        <is>
-          <t>incumbent_name</t>
-        </is>
-      </c>
-      <c r="B109" s="6" t="inlineStr">
-        <is>
-          <t>VARCHAR(200)</t>
-        </is>
-      </c>
-      <c r="C109" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D109" s="6" t="inlineStr"/>
-      <c r="E109" s="6" t="inlineStr"/>
-      <c r="F109" s="6" t="inlineStr"/>
-      <c r="G109" s="6" t="inlineStr">
-        <is>
-          <t>Current incumbent contractor name</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="5" t="inlineStr">
-        <is>
-          <t>recompete_details</t>
-        </is>
-      </c>
-      <c r="B110" s="5" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="C110" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D110" s="5" t="inlineStr"/>
-      <c r="E110" s="5" t="inlineStr"/>
-      <c r="F110" s="5" t="inlineStr"/>
-      <c r="G110" s="5" t="inlineStr">
-        <is>
-          <t>Recompete analysis details</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="6" t="inlineStr">
-        <is>
-          <t>scope_summary</t>
-        </is>
-      </c>
-      <c r="B111" s="6" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="C111" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D111" s="6" t="inlineStr"/>
-      <c r="E111" s="6" t="inlineStr"/>
-      <c r="F111" s="6" t="inlineStr"/>
-      <c r="G111" s="6" t="inlineStr">
-        <is>
-          <t>AI-generated scope summary</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="5" t="inlineStr">
-        <is>
-          <t>period_of_performance</t>
-        </is>
-      </c>
-      <c r="B112" s="5" t="inlineStr">
-        <is>
-          <t>VARCHAR(200)</t>
-        </is>
-      </c>
-      <c r="C112" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D112" s="5" t="inlineStr"/>
-      <c r="E112" s="5" t="inlineStr"/>
-      <c r="F112" s="5" t="inlineStr"/>
-      <c r="G112" s="5" t="inlineStr">
-        <is>
-          <t>Contract period of performance</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="6" t="inlineStr">
-        <is>
-          <t>labor_categories</t>
-        </is>
-      </c>
-      <c r="B113" s="6" t="inlineStr">
-        <is>
-          <t>JSON</t>
-        </is>
-      </c>
-      <c r="C113" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D113" s="6" t="inlineStr"/>
-      <c r="E113" s="6" t="inlineStr"/>
-      <c r="F113" s="6" t="inlineStr"/>
-      <c r="G113" s="6" t="inlineStr">
-        <is>
-          <t>JSON array of required labor categories</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="5" t="inlineStr">
-        <is>
-          <t>overall_confidence</t>
-        </is>
-      </c>
-      <c r="B114" s="5" t="inlineStr">
-        <is>
-          <t>ENUM(</t>
-        </is>
-      </c>
-      <c r="C114" s="5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D114" s="5" t="inlineStr"/>
-      <c r="E114" s="5" t="inlineStr"/>
-      <c r="F114" s="5" t="inlineStr"/>
-      <c r="G114" s="5" t="inlineStr">
-        <is>
-          <t>Confidence level of extraction (high/medium/low)</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="6" t="inlineStr">
-        <is>
-          <t>confidence_details</t>
-        </is>
-      </c>
-      <c r="B115" s="6" t="inlineStr">
-        <is>
-          <t>JSON</t>
-        </is>
-      </c>
-      <c r="C115" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D115" s="6" t="inlineStr"/>
-      <c r="E115" s="6" t="inlineStr"/>
-      <c r="F115" s="6" t="inlineStr"/>
-      <c r="G115" s="6" t="inlineStr">
-        <is>
-          <t>JSON breakdown of confidence by field</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="5" t="inlineStr">
-        <is>
-          <t>last_load_id</t>
-        </is>
-      </c>
-      <c r="B116" s="5" t="inlineStr">
-        <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="C116" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D116" s="5" t="inlineStr"/>
-      <c r="E116" s="5" t="inlineStr"/>
-      <c r="F116" s="5" t="inlineStr"/>
-      <c r="G116" s="5" t="inlineStr">
-        <is>
-          <t>FK to etl_load_log for traceability</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="6" t="inlineStr">
-        <is>
-          <t>extracted_at</t>
-        </is>
-      </c>
-      <c r="B117" s="6" t="inlineStr">
-        <is>
-          <t>DATETIME</t>
-        </is>
-      </c>
-      <c r="C117" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D117" s="6" t="inlineStr">
-        <is>
-          <t>CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="E117" s="6" t="inlineStr"/>
-      <c r="F117" s="6" t="inlineStr"/>
-      <c r="G117" s="6" t="inlineStr">
-        <is>
-          <t>When text was extracted</t>
-        </is>
-      </c>
-    </row>
-    <row r="118"/>
-    <row r="119">
-      <c r="A119" s="8" t="inlineStr">
-        <is>
-          <t>opportunity_intel_source</t>
-        </is>
-      </c>
-      <c r="B119" s="9" t="n"/>
-      <c r="C119" s="9" t="n"/>
-      <c r="D119" s="9" t="n"/>
-      <c r="E119" s="9" t="n"/>
-      <c r="F119" s="9" t="n"/>
-      <c r="G119" s="9" t="n"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="10" t="inlineStr">
-        <is>
-          <t>Column Name</t>
-        </is>
-      </c>
-      <c r="B120" s="10" t="inlineStr">
-        <is>
-          <t>Data Type</t>
-        </is>
-      </c>
-      <c r="C120" s="10" t="inlineStr">
-        <is>
-          <t>Nullable</t>
-        </is>
-      </c>
-      <c r="D120" s="10" t="inlineStr">
-        <is>
-          <t>Default</t>
-        </is>
-      </c>
-      <c r="E120" s="10" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="F120" s="10" t="inlineStr">
-        <is>
-          <t>Index</t>
-        </is>
-      </c>
-      <c r="G120" s="10" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="6" t="inlineStr">
-        <is>
-          <t>source_id</t>
-        </is>
-      </c>
-      <c r="B121" s="6" t="inlineStr">
-        <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="C121" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D121" s="6" t="inlineStr"/>
-      <c r="E121" s="6" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="F121" s="6" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G121" s="6" t="inlineStr">
-        <is>
-          <t>Auto-increment source reference ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="5" t="inlineStr">
-        <is>
-          <t>intel_id</t>
-        </is>
-      </c>
-      <c r="B122" s="5" t="inlineStr">
-        <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="C122" s="5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D122" s="5" t="inlineStr"/>
-      <c r="E122" s="5" t="inlineStr"/>
-      <c r="F122" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G122" s="5" t="inlineStr">
-        <is>
-          <t>Auto-increment intel record identifier</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="6" t="inlineStr">
-        <is>
-          <t>field_name</t>
-        </is>
-      </c>
-      <c r="B123" s="6" t="inlineStr">
-        <is>
-          <t>VARCHAR(50)</t>
-        </is>
-      </c>
-      <c r="C123" s="6" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D123" s="6" t="inlineStr"/>
-      <c r="E123" s="6" t="inlineStr"/>
-      <c r="F123" s="6" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G123" s="6" t="inlineStr">
-        <is>
-          <t>Changed field name</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="5" t="inlineStr">
-        <is>
-          <t>attachment_id</t>
-        </is>
-      </c>
-      <c r="B124" s="5" t="inlineStr">
-        <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="C124" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D124" s="5" t="inlineStr"/>
-      <c r="E124" s="5" t="inlineStr"/>
-      <c r="F124" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G124" s="5" t="inlineStr">
-        <is>
-          <t>Auto-increment attachment identifier</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="6" t="inlineStr">
-        <is>
-          <t>source_filename</t>
-        </is>
-      </c>
-      <c r="B125" s="6" t="inlineStr">
-        <is>
-          <t>VARCHAR(500)</t>
-        </is>
-      </c>
-      <c r="C125" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D125" s="6" t="inlineStr"/>
-      <c r="E125" s="6" t="inlineStr"/>
-      <c r="F125" s="6" t="inlineStr"/>
-      <c r="G125" s="6" t="inlineStr">
-        <is>
-          <t>Filename where text was found</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="5" t="inlineStr">
-        <is>
-          <t>page_number</t>
-        </is>
-      </c>
-      <c r="B126" s="5" t="inlineStr">
-        <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="C126" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D126" s="5" t="inlineStr"/>
-      <c r="E126" s="5" t="inlineStr"/>
-      <c r="F126" s="5" t="inlineStr"/>
-      <c r="G126" s="5" t="inlineStr">
-        <is>
-          <t>Page number in source document</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="6" t="inlineStr">
-        <is>
-          <t>char_offset_start</t>
-        </is>
-      </c>
-      <c r="B127" s="6" t="inlineStr">
-        <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="C127" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D127" s="6" t="inlineStr"/>
-      <c r="E127" s="6" t="inlineStr"/>
-      <c r="F127" s="6" t="inlineStr"/>
-      <c r="G127" s="6" t="inlineStr">
-        <is>
-          <t>Character offset start in extracted text</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="5" t="inlineStr">
-        <is>
-          <t>char_offset_end</t>
-        </is>
-      </c>
-      <c r="B128" s="5" t="inlineStr">
-        <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="C128" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D128" s="5" t="inlineStr"/>
-      <c r="E128" s="5" t="inlineStr"/>
-      <c r="F128" s="5" t="inlineStr"/>
-      <c r="G128" s="5" t="inlineStr">
-        <is>
-          <t>Character offset end in extracted text</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="6" t="inlineStr">
-        <is>
-          <t>matched_text</t>
-        </is>
-      </c>
-      <c r="B129" s="6" t="inlineStr">
-        <is>
-          <t>VARCHAR(500)</t>
-        </is>
-      </c>
-      <c r="C129" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D129" s="6" t="inlineStr"/>
-      <c r="E129" s="6" t="inlineStr"/>
-      <c r="F129" s="6" t="inlineStr"/>
-      <c r="G129" s="6" t="inlineStr">
-        <is>
-          <t>Exact text that matched the pattern</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="5" t="inlineStr">
-        <is>
-          <t>surrounding_context</t>
-        </is>
-      </c>
-      <c r="B130" s="5" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="C130" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D130" s="5" t="inlineStr"/>
-      <c r="E130" s="5" t="inlineStr"/>
-      <c r="F130" s="5" t="inlineStr"/>
-      <c r="G130" s="5" t="inlineStr">
-        <is>
-          <t>Text context around the match</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="6" t="inlineStr">
-        <is>
-          <t>pattern_name</t>
-        </is>
-      </c>
-      <c r="B131" s="6" t="inlineStr">
-        <is>
-          <t>VARCHAR(100)</t>
-        </is>
-      </c>
-      <c r="C131" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D131" s="6" t="inlineStr"/>
-      <c r="E131" s="6" t="inlineStr"/>
-      <c r="F131" s="6" t="inlineStr"/>
-      <c r="G131" s="6" t="inlineStr">
-        <is>
-          <t>Name of regex/heuristic pattern used</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="5" t="inlineStr">
-        <is>
-          <t>extraction_method</t>
-        </is>
-      </c>
-      <c r="B132" s="5" t="inlineStr">
-        <is>
-          <t>ENUM(</t>
-        </is>
-      </c>
-      <c r="C132" s="5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D132" s="5" t="inlineStr"/>
-      <c r="E132" s="5" t="inlineStr"/>
-      <c r="F132" s="5" t="inlineStr"/>
-      <c r="G132" s="5" t="inlineStr">
-        <is>
-          <t>How intel was extracted (keyword/heuristic/AI)</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="6" t="inlineStr">
-        <is>
-          <t>confidence</t>
-        </is>
-      </c>
-      <c r="B133" s="6" t="inlineStr">
-        <is>
-          <t>ENUM(</t>
-        </is>
-      </c>
-      <c r="C133" s="6" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D133" s="6" t="inlineStr"/>
-      <c r="E133" s="6" t="inlineStr"/>
-      <c r="F133" s="6" t="inlineStr"/>
-      <c r="G133" s="6" t="inlineStr">
-        <is>
-          <t>Confidence level for this source match</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="5" t="inlineStr">
-        <is>
-          <t>created_at</t>
-        </is>
-      </c>
-      <c r="B134" s="5" t="inlineStr">
-        <is>
-          <t>DATETIME</t>
-        </is>
-      </c>
-      <c r="C134" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D134" s="5" t="inlineStr">
-        <is>
-          <t>CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="E134" s="5" t="inlineStr"/>
-      <c r="F134" s="5" t="inlineStr"/>
-      <c r="G134" s="5" t="inlineStr">
-        <is>
-          <t>Row creation timestamp</t>
-        </is>
-      </c>
-    </row>
-    <row r="135"/>
-    <row r="136">
-      <c r="A136" s="8" t="inlineStr">
-        <is>
-          <t>opportunity_poc</t>
-        </is>
-      </c>
-      <c r="B136" s="9" t="n"/>
-      <c r="C136" s="9" t="n"/>
-      <c r="D136" s="9" t="n"/>
-      <c r="E136" s="9" t="n"/>
-      <c r="F136" s="9" t="n"/>
-      <c r="G136" s="9" t="n"/>
-    </row>
-    <row r="137">
-      <c r="A137" s="10" t="inlineStr">
-        <is>
-          <t>Column Name</t>
-        </is>
-      </c>
-      <c r="B137" s="10" t="inlineStr">
-        <is>
-          <t>Data Type</t>
-        </is>
-      </c>
-      <c r="C137" s="10" t="inlineStr">
-        <is>
-          <t>Nullable</t>
-        </is>
-      </c>
-      <c r="D137" s="10" t="inlineStr">
-        <is>
-          <t>Default</t>
-        </is>
-      </c>
-      <c r="E137" s="10" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="F137" s="10" t="inlineStr">
-        <is>
-          <t>Index</t>
-        </is>
-      </c>
-      <c r="G137" s="10" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="6" t="inlineStr">
-        <is>
-          <t>poc_id</t>
-        </is>
-      </c>
-      <c r="B138" s="6" t="inlineStr">
-        <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="C138" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D138" s="6" t="inlineStr"/>
-      <c r="E138" s="6" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="F138" s="6" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G138" s="6" t="inlineStr">
-        <is>
-          <t>Auto-increment POC identifier</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="5" t="inlineStr">
-        <is>
-          <t>notice_id</t>
-        </is>
-      </c>
-      <c r="B139" s="5" t="inlineStr">
-        <is>
-          <t>VARCHAR(100)</t>
-        </is>
-      </c>
-      <c r="C139" s="5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D139" s="5" t="inlineStr"/>
-      <c r="E139" s="5" t="inlineStr"/>
-      <c r="F139" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G139" s="5" t="inlineStr">
-        <is>
-          <t>SAM.gov opportunity identifier</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="6" t="inlineStr">
-        <is>
-          <t>officer_id</t>
-        </is>
-      </c>
-      <c r="B140" s="6" t="inlineStr">
-        <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="C140" s="6" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D140" s="6" t="inlineStr"/>
-      <c r="E140" s="6" t="inlineStr"/>
-      <c r="F140" s="6" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G140" s="6" t="inlineStr">
-        <is>
-          <t>FK to contracting_officer</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="5" t="inlineStr">
-        <is>
-          <t>poc_type</t>
-        </is>
-      </c>
-      <c r="B141" s="5" t="inlineStr">
-        <is>
-          <t>VARCHAR(20)</t>
-        </is>
-      </c>
-      <c r="C141" s="5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D141" s="5" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="E141" s="5" t="inlineStr"/>
-      <c r="F141" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G141" s="5" t="inlineStr">
-        <is>
-          <t>Contact type (PRIMARY, SECONDARY)</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="6" t="inlineStr">
-        <is>
-          <t>created_at</t>
-        </is>
-      </c>
-      <c r="B142" s="6" t="inlineStr">
-        <is>
-          <t>DATETIME</t>
-        </is>
-      </c>
-      <c r="C142" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D142" s="6" t="inlineStr">
-        <is>
-          <t>CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="E142" s="6" t="inlineStr"/>
-      <c r="F142" s="6" t="inlineStr"/>
-      <c r="G142" s="6" t="inlineStr">
-        <is>
-          <t>Row creation timestamp</t>
-        </is>
-      </c>
-    </row>
-    <row r="143"/>
-    <row r="144">
-      <c r="A144" s="8" t="inlineStr">
-        <is>
-          <t>contracting_officer</t>
-        </is>
-      </c>
-      <c r="B144" s="9" t="n"/>
-      <c r="C144" s="9" t="n"/>
-      <c r="D144" s="9" t="n"/>
-      <c r="E144" s="9" t="n"/>
-      <c r="F144" s="9" t="n"/>
-      <c r="G144" s="9" t="n"/>
-    </row>
-    <row r="145">
-      <c r="A145" s="10" t="inlineStr">
-        <is>
-          <t>Column Name</t>
-        </is>
-      </c>
-      <c r="B145" s="10" t="inlineStr">
-        <is>
-          <t>Data Type</t>
-        </is>
-      </c>
-      <c r="C145" s="10" t="inlineStr">
-        <is>
-          <t>Nullable</t>
-        </is>
-      </c>
-      <c r="D145" s="10" t="inlineStr">
-        <is>
-          <t>Default</t>
-        </is>
-      </c>
-      <c r="E145" s="10" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="F145" s="10" t="inlineStr">
-        <is>
-          <t>Index</t>
-        </is>
-      </c>
-      <c r="G145" s="10" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="6" t="inlineStr">
-        <is>
-          <t>officer_id</t>
-        </is>
-      </c>
-      <c r="B146" s="6" t="inlineStr">
-        <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="C146" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D146" s="6" t="inlineStr"/>
-      <c r="E146" s="6" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="F146" s="6" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G146" s="6" t="inlineStr">
-        <is>
-          <t>FK to contracting_officer</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="5" t="inlineStr">
-        <is>
-          <t>full_name</t>
-        </is>
-      </c>
-      <c r="B147" s="5" t="inlineStr">
-        <is>
-          <t>VARCHAR(500)</t>
-        </is>
-      </c>
-      <c r="C147" s="5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D147" s="5" t="inlineStr"/>
-      <c r="E147" s="5" t="inlineStr"/>
-      <c r="F147" s="5" t="inlineStr"/>
-      <c r="G147" s="5" t="inlineStr">
-        <is>
-          <t>Officer full name</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="6" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="B148" s="6" t="inlineStr">
-        <is>
-          <t>VARCHAR(200)</t>
-        </is>
-      </c>
-      <c r="C148" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D148" s="6" t="inlineStr"/>
-      <c r="E148" s="6" t="inlineStr"/>
-      <c r="F148" s="6" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G148" s="6" t="inlineStr">
-        <is>
-          <t>User email address</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="5" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="B149" s="5" t="inlineStr">
-        <is>
-          <t>VARCHAR(100)</t>
-        </is>
-      </c>
-      <c r="C149" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D149" s="5" t="inlineStr"/>
-      <c r="E149" s="5" t="inlineStr"/>
-      <c r="F149" s="5" t="inlineStr"/>
-      <c r="G149" s="5" t="inlineStr">
-        <is>
-          <t>Contact phone number</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="6" t="inlineStr">
-        <is>
-          <t>fax</t>
-        </is>
-      </c>
-      <c r="B150" s="6" t="inlineStr">
-        <is>
-          <t>VARCHAR(100)</t>
-        </is>
-      </c>
-      <c r="C150" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D150" s="6" t="inlineStr"/>
-      <c r="E150" s="6" t="inlineStr"/>
-      <c r="F150" s="6" t="inlineStr"/>
-      <c r="G150" s="6" t="inlineStr">
-        <is>
-          <t>Fax number</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="5" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="B151" s="5" t="inlineStr">
-        <is>
-          <t>VARCHAR(200)</t>
-        </is>
-      </c>
-      <c r="C151" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D151" s="5" t="inlineStr"/>
-      <c r="E151" s="5" t="inlineStr"/>
-      <c r="F151" s="5" t="inlineStr"/>
-      <c r="G151" s="5" t="inlineStr">
-        <is>
-          <t>Opportunity title</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="6" t="inlineStr">
-        <is>
-          <t>department_name</t>
-        </is>
-      </c>
-      <c r="B152" s="6" t="inlineStr">
-        <is>
-          <t>VARCHAR(200)</t>
-        </is>
-      </c>
-      <c r="C152" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D152" s="6" t="inlineStr"/>
-      <c r="E152" s="6" t="inlineStr"/>
-      <c r="F152" s="6" t="inlineStr"/>
-      <c r="G152" s="6" t="inlineStr">
-        <is>
-          <t>Issuing federal department</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="5" t="inlineStr">
-        <is>
-          <t>office_name</t>
-        </is>
-      </c>
-      <c r="B153" s="5" t="inlineStr">
-        <is>
-          <t>VARCHAR(200)</t>
-        </is>
-      </c>
-      <c r="C153" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D153" s="5" t="inlineStr"/>
-      <c r="E153" s="5" t="inlineStr"/>
-      <c r="F153" s="5" t="inlineStr"/>
-      <c r="G153" s="5" t="inlineStr"/>
-    </row>
-    <row r="154">
-      <c r="A154" s="6" t="inlineStr">
-        <is>
-          <t>officer_type</t>
-        </is>
-      </c>
-      <c r="B154" s="6" t="inlineStr">
-        <is>
-          <t>VARCHAR(50)</t>
-        </is>
-      </c>
-      <c r="C154" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D154" s="6" t="inlineStr"/>
-      <c r="E154" s="6" t="inlineStr"/>
-      <c r="F154" s="6" t="inlineStr"/>
-      <c r="G154" s="6" t="inlineStr">
-        <is>
-          <t>Type (Contracting Officer, Specialist, etc.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="5" t="inlineStr">
-        <is>
-          <t>created_at</t>
-        </is>
-      </c>
-      <c r="B155" s="5" t="inlineStr">
-        <is>
-          <t>DATETIME</t>
-        </is>
-      </c>
-      <c r="C155" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D155" s="5" t="inlineStr">
-        <is>
-          <t>CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="E155" s="5" t="inlineStr"/>
-      <c r="F155" s="5" t="inlineStr"/>
-      <c r="G155" s="5" t="inlineStr">
-        <is>
-          <t>Row creation timestamp</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="6" t="inlineStr">
-        <is>
-          <t>updated_at</t>
-        </is>
-      </c>
-      <c r="B156" s="6" t="inlineStr">
-        <is>
-          <t>DATETIME</t>
-        </is>
-      </c>
-      <c r="C156" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D156" s="6" t="inlineStr">
-        <is>
-          <t>CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="E156" s="6" t="inlineStr"/>
-      <c r="F156" s="6" t="inlineStr"/>
-      <c r="G156" s="6" t="inlineStr">
-        <is>
           <t>Row last-update timestamp</t>
         </is>
       </c>
     </row>
-    <row r="157"/>
+    <row r="102"/>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A93:G93"/>
-    <mergeCell ref="A61:G61"/>
-    <mergeCell ref="A119:G119"/>
+  <mergeCells count="6">
+    <mergeCell ref="A89:G89"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A144:G144"/>
-    <mergeCell ref="A136:G136"/>
-    <mergeCell ref="A71:G71"/>
-    <mergeCell ref="A51:G51"/>
+    <mergeCell ref="A53:G53"/>
+    <mergeCell ref="A81:G81"/>
+    <mergeCell ref="A73:G73"/>
+    <mergeCell ref="A63:G63"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4688,7 +3271,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G161"/>
+  <dimension ref="A1:G180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -5869,7 +4452,7 @@
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>usaspending_award</t>
+          <t>federal_organization</t>
         </is>
       </c>
       <c r="B47" s="9" t="n"/>
@@ -5919,17 +4502,17 @@
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>generated_unique_award_id</t>
+          <t>fh_org_id</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>VARCHAR(100)</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr"/>
@@ -5945,19 +4528,19 @@
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>USASpending unique award identifier</t>
+          <t>Federal hierarchy organization ID</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>piid</t>
+          <t>fh_org_name</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>VARCHAR(50)</t>
+          <t>VARCHAR(500)</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
@@ -5967,26 +4550,22 @@
       </c>
       <c r="D50" s="5" t="inlineStr"/>
       <c r="E50" s="5" t="inlineStr"/>
-      <c r="F50" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="F50" s="5" t="inlineStr"/>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>Procurement Instrument Identifier</t>
+          <t>Federal organization name</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>fain</t>
+          <t>fh_org_type</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>VARCHAR(30)</t>
+          <t>VARCHAR(50)</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
@@ -5996,22 +4575,26 @@
       </c>
       <c r="D51" s="6" t="inlineStr"/>
       <c r="E51" s="6" t="inlineStr"/>
-      <c r="F51" s="6" t="inlineStr"/>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>Federal Award Identification Number</t>
+          <t>Organization type (department, agency, office)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>uri</t>
+          <t>description</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>VARCHAR(70)</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
@@ -6024,19 +4607,19 @@
       <c r="F52" s="5" t="inlineStr"/>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>Unique Record Identifier</t>
+          <t>Description text</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>award_type</t>
+          <t>status</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>VARCHAR(50)</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
@@ -6046,22 +4629,26 @@
       </c>
       <c r="D53" s="6" t="inlineStr"/>
       <c r="E53" s="6" t="inlineStr"/>
-      <c r="F53" s="6" t="inlineStr"/>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>Award type (contract, grant, etc.)</t>
+          <t>Organization status</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>award_description</t>
+          <t>agency_code</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
@@ -6071,22 +4658,26 @@
       </c>
       <c r="D54" s="5" t="inlineStr"/>
       <c r="E54" s="5" t="inlineStr"/>
-      <c r="F54" s="5" t="inlineStr"/>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>Award description text</t>
+          <t>Agency code identifier</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>recipient_name</t>
+          <t>oldfpds_office_code</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>VARCHAR(200)</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
@@ -6099,19 +4690,19 @@
       <c r="F55" s="6" t="inlineStr"/>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>Recipient/incumbent name</t>
+          <t>Legacy FPDS office code</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>recipient_uei</t>
+          <t>cgac</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>VARCHAR(12)</t>
+          <t>VARCHAR(10)</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
@@ -6128,19 +4719,19 @@
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>Recipient UEI</t>
+          <t>Common Government-wide Accounting Classification</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>recipient_parent_name</t>
+          <t>parent_org_id</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>VARCHAR(200)</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
@@ -6150,22 +4741,26 @@
       </c>
       <c r="D57" s="6" t="inlineStr"/>
       <c r="E57" s="6" t="inlineStr"/>
-      <c r="F57" s="6" t="inlineStr"/>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>Parent organization name</t>
+          <t>Parent organization in hierarchy</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>recipient_parent_uei</t>
+          <t>level</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>VARCHAR(12)</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
@@ -6178,19 +4773,19 @@
       <c r="F58" s="5" t="inlineStr"/>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>Parent organization UEI</t>
+          <t>Depth level in hierarchy tree</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>total_obligation</t>
+          <t>created_date</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>DECIMAL(15</t>
+          <t>DATE</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
@@ -6201,21 +4796,17 @@
       <c r="D59" s="6" t="inlineStr"/>
       <c r="E59" s="6" t="inlineStr"/>
       <c r="F59" s="6" t="inlineStr"/>
-      <c r="G59" s="6" t="inlineStr">
-        <is>
-          <t>Total dollars obligated</t>
-        </is>
-      </c>
+      <c r="G59" s="6" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>base_and_all_options_value</t>
+          <t>last_modified_date</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>DECIMAL(15</t>
+          <t>DATE</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
@@ -6228,19 +4819,19 @@
       <c r="F60" s="5" t="inlineStr"/>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>Total value including all options</t>
+          <t>Last modification date</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>start_date</t>
+          <t>record_hash</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>DATE</t>
+          <t>CHAR(64)</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
@@ -6257,19 +4848,19 @@
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
-          <t>PSC code effective start date</t>
+          <t>SHA-256 hash for change detection</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>end_date</t>
+          <t>first_loaded_at</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>DATE</t>
+          <t>DATETIME</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
@@ -6277,28 +4868,28 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="D62" s="5" t="inlineStr"/>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
       <c r="E62" s="5" t="inlineStr"/>
-      <c r="F62" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="F62" s="5" t="inlineStr"/>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>PSC code end date (null if current)</t>
+          <t>Timestamp of initial ETL load</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>last_modified_date</t>
+          <t>last_loaded_at</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>DATE</t>
+          <t>DATETIME</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
@@ -6306,28 +4897,28 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="D63" s="6" t="inlineStr"/>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
       <c r="E63" s="6" t="inlineStr"/>
-      <c r="F63" s="6" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="F63" s="6" t="inlineStr"/>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>Last modification date</t>
+          <t>Timestamp of most recent ETL load</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>awarding_agency_name</t>
+          <t>last_load_id</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>VARCHAR(200)</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
@@ -6340,1256 +4931,1268 @@
       <c r="F64" s="5" t="inlineStr"/>
       <c r="G64" s="5" t="inlineStr">
         <is>
+          <t>FK to etl_load_log for traceability</t>
+        </is>
+      </c>
+    </row>
+    <row r="65"/>
+    <row r="66">
+      <c r="A66" s="8" t="inlineStr">
+        <is>
+          <t>usaspending_award</t>
+        </is>
+      </c>
+      <c r="B66" s="9" t="n"/>
+      <c r="C66" s="9" t="n"/>
+      <c r="D66" s="9" t="n"/>
+      <c r="E66" s="9" t="n"/>
+      <c r="F66" s="9" t="n"/>
+      <c r="G66" s="9" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="10" t="inlineStr">
+        <is>
+          <t>Column Name</t>
+        </is>
+      </c>
+      <c r="B67" s="10" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="C67" s="10" t="inlineStr">
+        <is>
+          <t>Nullable</t>
+        </is>
+      </c>
+      <c r="D67" s="10" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="E67" s="10" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="F67" s="10" t="inlineStr">
+        <is>
+          <t>Index</t>
+        </is>
+      </c>
+      <c r="G67" s="10" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>generated_unique_award_id</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>VARCHAR(100)</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr"/>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="F68" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G68" s="6" t="inlineStr">
+        <is>
+          <t>USASpending unique award identifier</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>piid</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>VARCHAR(50)</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr"/>
+      <c r="E69" s="5" t="inlineStr"/>
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>Procurement Instrument Identifier</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>fain</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>VARCHAR(30)</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr"/>
+      <c r="E70" s="6" t="inlineStr"/>
+      <c r="F70" s="6" t="inlineStr"/>
+      <c r="G70" s="6" t="inlineStr">
+        <is>
+          <t>Federal Award Identification Number</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>uri</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>VARCHAR(70)</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr"/>
+      <c r="E71" s="5" t="inlineStr"/>
+      <c r="F71" s="5" t="inlineStr"/>
+      <c r="G71" s="5" t="inlineStr">
+        <is>
+          <t>Unique Record Identifier</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>award_type</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>VARCHAR(50)</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="inlineStr"/>
+      <c r="E72" s="6" t="inlineStr"/>
+      <c r="F72" s="6" t="inlineStr"/>
+      <c r="G72" s="6" t="inlineStr">
+        <is>
+          <t>Award type (contract, grant, etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>award_description</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr"/>
+      <c r="E73" s="5" t="inlineStr"/>
+      <c r="F73" s="5" t="inlineStr"/>
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>Award description text</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>recipient_name</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>VARCHAR(200)</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr"/>
+      <c r="E74" s="6" t="inlineStr"/>
+      <c r="F74" s="6" t="inlineStr"/>
+      <c r="G74" s="6" t="inlineStr">
+        <is>
+          <t>Recipient/incumbent name</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>recipient_uei</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>VARCHAR(12)</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr"/>
+      <c r="E75" s="5" t="inlineStr"/>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="inlineStr">
+        <is>
+          <t>Recipient UEI</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>recipient_parent_name</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>VARCHAR(200)</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr"/>
+      <c r="E76" s="6" t="inlineStr"/>
+      <c r="F76" s="6" t="inlineStr"/>
+      <c r="G76" s="6" t="inlineStr">
+        <is>
+          <t>Parent organization name</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>recipient_parent_uei</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>VARCHAR(12)</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr"/>
+      <c r="E77" s="5" t="inlineStr"/>
+      <c r="F77" s="5" t="inlineStr"/>
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t>Parent organization UEI</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>total_obligation</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>DECIMAL(15</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr"/>
+      <c r="E78" s="6" t="inlineStr"/>
+      <c r="F78" s="6" t="inlineStr"/>
+      <c r="G78" s="6" t="inlineStr">
+        <is>
+          <t>Total dollars obligated</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>base_and_all_options_value</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>DECIMAL(15</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr"/>
+      <c r="E79" s="5" t="inlineStr"/>
+      <c r="F79" s="5" t="inlineStr"/>
+      <c r="G79" s="5" t="inlineStr">
+        <is>
+          <t>Total value including all options</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>start_date</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr"/>
+      <c r="E80" s="6" t="inlineStr"/>
+      <c r="F80" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G80" s="6" t="inlineStr">
+        <is>
+          <t>PSC code effective start date</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>end_date</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr"/>
+      <c r="E81" s="5" t="inlineStr"/>
+      <c r="F81" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="inlineStr">
+        <is>
+          <t>PSC code end date (null if current)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>last_modified_date</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr"/>
+      <c r="E82" s="6" t="inlineStr"/>
+      <c r="F82" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G82" s="6" t="inlineStr">
+        <is>
+          <t>Last modification date</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>awarding_agency_name</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>VARCHAR(200)</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="inlineStr"/>
+      <c r="E83" s="5" t="inlineStr"/>
+      <c r="F83" s="5" t="inlineStr"/>
+      <c r="G83" s="5" t="inlineStr">
+        <is>
           <t>Awarding agency name</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="6" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr">
         <is>
           <t>awarding_sub_agency_name</t>
         </is>
       </c>
-      <c r="B65" s="6" t="inlineStr">
+      <c r="B84" s="6" t="inlineStr">
         <is>
           <t>VARCHAR(200)</t>
         </is>
       </c>
-      <c r="C65" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D65" s="6" t="inlineStr"/>
-      <c r="E65" s="6" t="inlineStr"/>
-      <c r="F65" s="6" t="inlineStr"/>
-      <c r="G65" s="6" t="inlineStr">
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="inlineStr"/>
+      <c r="E84" s="6" t="inlineStr"/>
+      <c r="F84" s="6" t="inlineStr"/>
+      <c r="G84" s="6" t="inlineStr">
         <is>
           <t>Awarding sub-agency name</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="5" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
         <is>
           <t>funding_agency_name</t>
         </is>
       </c>
-      <c r="B66" s="5" t="inlineStr">
+      <c r="B85" s="5" t="inlineStr">
         <is>
           <t>VARCHAR(200)</t>
         </is>
       </c>
-      <c r="C66" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D66" s="5" t="inlineStr"/>
-      <c r="E66" s="5" t="inlineStr"/>
-      <c r="F66" s="5" t="inlineStr"/>
-      <c r="G66" s="5" t="inlineStr">
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="inlineStr"/>
+      <c r="E85" s="5" t="inlineStr"/>
+      <c r="F85" s="5" t="inlineStr"/>
+      <c r="G85" s="5" t="inlineStr">
         <is>
           <t>Funding agency name</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="6" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
         <is>
           <t>naics_code</t>
         </is>
       </c>
-      <c r="B67" s="6" t="inlineStr">
+      <c r="B86" s="6" t="inlineStr">
         <is>
           <t>VARCHAR(6)</t>
         </is>
       </c>
-      <c r="C67" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D67" s="6" t="inlineStr"/>
-      <c r="E67" s="6" t="inlineStr"/>
-      <c r="F67" s="6" t="inlineStr">
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr"/>
+      <c r="E86" s="6" t="inlineStr"/>
+      <c r="F86" s="6" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="G67" s="6" t="inlineStr">
+      <c r="G86" s="6" t="inlineStr">
         <is>
           <t>NAICS industry classification code</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="5" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
         <is>
           <t>naics_description</t>
         </is>
       </c>
-      <c r="B68" s="5" t="inlineStr">
+      <c r="B87" s="5" t="inlineStr">
         <is>
           <t>VARCHAR(500)</t>
         </is>
       </c>
-      <c r="C68" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D68" s="5" t="inlineStr"/>
-      <c r="E68" s="5" t="inlineStr"/>
-      <c r="F68" s="5" t="inlineStr"/>
-      <c r="G68" s="5" t="inlineStr">
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D87" s="5" t="inlineStr"/>
+      <c r="E87" s="5" t="inlineStr"/>
+      <c r="F87" s="5" t="inlineStr"/>
+      <c r="G87" s="5" t="inlineStr">
         <is>
           <t>NAICS code description</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="6" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="6" t="inlineStr">
         <is>
           <t>psc_code</t>
         </is>
       </c>
-      <c r="B69" s="6" t="inlineStr">
+      <c r="B88" s="6" t="inlineStr">
         <is>
           <t>VARCHAR(10)</t>
         </is>
       </c>
-      <c r="C69" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D69" s="6" t="inlineStr"/>
-      <c r="E69" s="6" t="inlineStr"/>
-      <c r="F69" s="6" t="inlineStr"/>
-      <c r="G69" s="6" t="inlineStr">
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr"/>
+      <c r="E88" s="6" t="inlineStr"/>
+      <c r="F88" s="6" t="inlineStr"/>
+      <c r="G88" s="6" t="inlineStr">
         <is>
           <t>Product/Service Code</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
         <is>
           <t>type_of_set_aside</t>
         </is>
       </c>
-      <c r="B70" s="5" t="inlineStr">
+      <c r="B89" s="5" t="inlineStr">
         <is>
           <t>VARCHAR(100)</t>
         </is>
       </c>
-      <c r="C70" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D70" s="5" t="inlineStr"/>
-      <c r="E70" s="5" t="inlineStr"/>
-      <c r="F70" s="5" t="inlineStr">
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="inlineStr"/>
+      <c r="E89" s="5" t="inlineStr"/>
+      <c r="F89" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="G70" s="5" t="inlineStr">
+      <c r="G89" s="5" t="inlineStr">
         <is>
           <t>Set-aside type code</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="6" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="6" t="inlineStr">
         <is>
           <t>type_of_set_aside_description</t>
         </is>
       </c>
-      <c r="B71" s="6" t="inlineStr">
+      <c r="B90" s="6" t="inlineStr">
         <is>
           <t>VARCHAR(200)</t>
         </is>
       </c>
-      <c r="C71" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D71" s="6" t="inlineStr"/>
-      <c r="E71" s="6" t="inlineStr"/>
-      <c r="F71" s="6" t="inlineStr"/>
-      <c r="G71" s="6" t="inlineStr">
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D90" s="6" t="inlineStr"/>
+      <c r="E90" s="6" t="inlineStr"/>
+      <c r="F90" s="6" t="inlineStr"/>
+      <c r="G90" s="6" t="inlineStr">
         <is>
           <t>Set-aside description</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="5" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="5" t="inlineStr">
         <is>
           <t>pop_state</t>
         </is>
       </c>
-      <c r="B72" s="5" t="inlineStr">
+      <c r="B91" s="5" t="inlineStr">
         <is>
           <t>VARCHAR(6)</t>
         </is>
       </c>
-      <c r="C72" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D72" s="5" t="inlineStr"/>
-      <c r="E72" s="5" t="inlineStr"/>
-      <c r="F72" s="5" t="inlineStr"/>
-      <c r="G72" s="5" t="inlineStr">
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="inlineStr"/>
+      <c r="E91" s="5" t="inlineStr"/>
+      <c r="F91" s="5" t="inlineStr"/>
+      <c r="G91" s="5" t="inlineStr">
         <is>
           <t>Place of performance state (ISO 3166-2)</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="6" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="6" t="inlineStr">
         <is>
           <t>pop_country</t>
         </is>
       </c>
-      <c r="B73" s="6" t="inlineStr">
+      <c r="B92" s="6" t="inlineStr">
         <is>
           <t>VARCHAR(3)</t>
         </is>
       </c>
-      <c r="C73" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D73" s="6" t="inlineStr"/>
-      <c r="E73" s="6" t="inlineStr"/>
-      <c r="F73" s="6" t="inlineStr"/>
-      <c r="G73" s="6" t="inlineStr">
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D92" s="6" t="inlineStr"/>
+      <c r="E92" s="6" t="inlineStr"/>
+      <c r="F92" s="6" t="inlineStr"/>
+      <c r="G92" s="6" t="inlineStr">
         <is>
           <t>Place of performance country code</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="5" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
         <is>
           <t>pop_zip</t>
         </is>
       </c>
-      <c r="B74" s="5" t="inlineStr">
+      <c r="B93" s="5" t="inlineStr">
         <is>
           <t>VARCHAR(10)</t>
         </is>
       </c>
-      <c r="C74" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D74" s="5" t="inlineStr"/>
-      <c r="E74" s="5" t="inlineStr"/>
-      <c r="F74" s="5" t="inlineStr"/>
-      <c r="G74" s="5" t="inlineStr">
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr"/>
+      <c r="E93" s="5" t="inlineStr"/>
+      <c r="F93" s="5" t="inlineStr"/>
+      <c r="G93" s="5" t="inlineStr">
         <is>
           <t>Place of performance ZIP code</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="6" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="6" t="inlineStr">
         <is>
           <t>pop_city</t>
         </is>
       </c>
-      <c r="B75" s="6" t="inlineStr">
+      <c r="B94" s="6" t="inlineStr">
         <is>
           <t>VARCHAR(100)</t>
         </is>
       </c>
-      <c r="C75" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D75" s="6" t="inlineStr"/>
-      <c r="E75" s="6" t="inlineStr"/>
-      <c r="F75" s="6" t="inlineStr"/>
-      <c r="G75" s="6" t="inlineStr">
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D94" s="6" t="inlineStr"/>
+      <c r="E94" s="6" t="inlineStr"/>
+      <c r="F94" s="6" t="inlineStr"/>
+      <c r="G94" s="6" t="inlineStr">
         <is>
           <t>Place of performance city</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="5" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="5" t="inlineStr">
         <is>
           <t>solicitation_identifier</t>
         </is>
       </c>
-      <c r="B76" s="5" t="inlineStr">
+      <c r="B95" s="5" t="inlineStr">
         <is>
           <t>VARCHAR(100)</t>
         </is>
       </c>
-      <c r="C76" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D76" s="5" t="inlineStr"/>
-      <c r="E76" s="5" t="inlineStr"/>
-      <c r="F76" s="5" t="inlineStr">
+      <c r="C95" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D95" s="5" t="inlineStr"/>
+      <c r="E95" s="5" t="inlineStr"/>
+      <c r="F95" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="G76" s="5" t="inlineStr">
+      <c r="G95" s="5" t="inlineStr">
         <is>
           <t>Linked solicitation number</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="6" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="6" t="inlineStr">
         <is>
           <t>fiscal_year</t>
         </is>
       </c>
-      <c r="B77" s="6" t="inlineStr">
+      <c r="B96" s="6" t="inlineStr">
         <is>
           <t>SMALLINT</t>
         </is>
       </c>
-      <c r="C77" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D77" s="6" t="inlineStr"/>
-      <c r="E77" s="6" t="inlineStr"/>
-      <c r="F77" s="6" t="inlineStr">
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D96" s="6" t="inlineStr"/>
+      <c r="E96" s="6" t="inlineStr"/>
+      <c r="F96" s="6" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="G77" s="6" t="inlineStr">
+      <c r="G96" s="6" t="inlineStr">
         <is>
           <t>Federal fiscal year</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="5" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="5" t="inlineStr">
         <is>
           <t>fpds_enriched_at</t>
         </is>
       </c>
-      <c r="B78" s="5" t="inlineStr">
+      <c r="B97" s="5" t="inlineStr">
         <is>
           <t>DATETIME</t>
         </is>
       </c>
-      <c r="C78" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D78" s="5" t="inlineStr"/>
-      <c r="E78" s="5" t="inlineStr"/>
-      <c r="F78" s="5" t="inlineStr">
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D97" s="5" t="inlineStr"/>
+      <c r="E97" s="5" t="inlineStr"/>
+      <c r="F97" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="G78" s="5" t="inlineStr">
+      <c r="G97" s="5" t="inlineStr">
         <is>
           <t>When FPDS enrichment was applied</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="6" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="6" t="inlineStr">
         <is>
           <t>record_hash</t>
         </is>
       </c>
-      <c r="B79" s="6" t="inlineStr">
+      <c r="B98" s="6" t="inlineStr">
         <is>
           <t>CHAR(64)</t>
         </is>
       </c>
-      <c r="C79" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D79" s="6" t="inlineStr"/>
-      <c r="E79" s="6" t="inlineStr"/>
-      <c r="F79" s="6" t="inlineStr"/>
-      <c r="G79" s="6" t="inlineStr">
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D98" s="6" t="inlineStr"/>
+      <c r="E98" s="6" t="inlineStr"/>
+      <c r="F98" s="6" t="inlineStr"/>
+      <c r="G98" s="6" t="inlineStr">
         <is>
           <t>SHA-256 hash for change detection</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="5" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="5" t="inlineStr">
         <is>
           <t>last_load_id</t>
         </is>
       </c>
-      <c r="B80" s="5" t="inlineStr">
+      <c r="B99" s="5" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="C80" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D80" s="5" t="inlineStr"/>
-      <c r="E80" s="5" t="inlineStr"/>
-      <c r="F80" s="5" t="inlineStr"/>
-      <c r="G80" s="5" t="inlineStr">
+      <c r="C99" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D99" s="5" t="inlineStr"/>
+      <c r="E99" s="5" t="inlineStr"/>
+      <c r="F99" s="5" t="inlineStr"/>
+      <c r="G99" s="5" t="inlineStr">
         <is>
           <t>FK to etl_load_log for traceability</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="6" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="6" t="inlineStr">
         <is>
           <t>first_loaded_at</t>
         </is>
       </c>
-      <c r="B81" s="6" t="inlineStr">
+      <c r="B100" s="6" t="inlineStr">
         <is>
           <t>DATETIME</t>
         </is>
       </c>
-      <c r="C81" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D81" s="6" t="inlineStr">
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D100" s="6" t="inlineStr">
         <is>
           <t>CURRENT_TIMESTAMP</t>
         </is>
       </c>
-      <c r="E81" s="6" t="inlineStr"/>
-      <c r="F81" s="6" t="inlineStr"/>
-      <c r="G81" s="6" t="inlineStr">
+      <c r="E100" s="6" t="inlineStr"/>
+      <c r="F100" s="6" t="inlineStr"/>
+      <c r="G100" s="6" t="inlineStr">
         <is>
           <t>Timestamp of initial ETL load</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="5" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="5" t="inlineStr">
         <is>
           <t>last_loaded_at</t>
         </is>
       </c>
-      <c r="B82" s="5" t="inlineStr">
+      <c r="B101" s="5" t="inlineStr">
         <is>
           <t>DATETIME</t>
         </is>
       </c>
-      <c r="C82" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D82" s="5" t="inlineStr">
+      <c r="C101" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D101" s="5" t="inlineStr">
         <is>
           <t>CURRENT_TIMESTAMP</t>
         </is>
       </c>
-      <c r="E82" s="5" t="inlineStr"/>
-      <c r="F82" s="5" t="inlineStr"/>
-      <c r="G82" s="5" t="inlineStr">
+      <c r="E101" s="5" t="inlineStr"/>
+      <c r="F101" s="5" t="inlineStr"/>
+      <c r="G101" s="5" t="inlineStr">
         <is>
           <t>Timestamp of most recent ETL load</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="6" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="6" t="inlineStr">
         <is>
           <t>deleted_at</t>
         </is>
       </c>
-      <c r="B83" s="6" t="inlineStr">
+      <c r="B102" s="6" t="inlineStr">
         <is>
           <t>DATETIME</t>
         </is>
       </c>
-      <c r="C83" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D83" s="6" t="inlineStr"/>
-      <c r="E83" s="6" t="inlineStr"/>
-      <c r="F83" s="6" t="inlineStr"/>
-      <c r="G83" s="6" t="inlineStr">
+      <c r="C102" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D102" s="6" t="inlineStr"/>
+      <c r="E102" s="6" t="inlineStr"/>
+      <c r="F102" s="6" t="inlineStr"/>
+      <c r="G102" s="6" t="inlineStr">
         <is>
           <t>Soft-delete timestamp (preserves FK refs)</t>
         </is>
       </c>
     </row>
-    <row r="84"/>
-    <row r="85">
-      <c r="A85" s="8" t="inlineStr">
+    <row r="103"/>
+    <row r="104">
+      <c r="A104" s="8" t="inlineStr">
         <is>
           <t>usaspending_transaction</t>
         </is>
       </c>
-      <c r="B85" s="9" t="n"/>
-      <c r="C85" s="9" t="n"/>
-      <c r="D85" s="9" t="n"/>
-      <c r="E85" s="9" t="n"/>
-      <c r="F85" s="9" t="n"/>
-      <c r="G85" s="9" t="n"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="10" t="inlineStr">
+      <c r="B104" s="9" t="n"/>
+      <c r="C104" s="9" t="n"/>
+      <c r="D104" s="9" t="n"/>
+      <c r="E104" s="9" t="n"/>
+      <c r="F104" s="9" t="n"/>
+      <c r="G104" s="9" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="10" t="inlineStr">
         <is>
           <t>Column Name</t>
         </is>
       </c>
-      <c r="B86" s="10" t="inlineStr">
+      <c r="B105" s="10" t="inlineStr">
         <is>
           <t>Data Type</t>
         </is>
       </c>
-      <c r="C86" s="10" t="inlineStr">
+      <c r="C105" s="10" t="inlineStr">
         <is>
           <t>Nullable</t>
         </is>
       </c>
-      <c r="D86" s="10" t="inlineStr">
+      <c r="D105" s="10" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="E86" s="10" t="inlineStr">
+      <c r="E105" s="10" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="F86" s="10" t="inlineStr">
+      <c r="F105" s="10" t="inlineStr">
         <is>
           <t>Index</t>
         </is>
       </c>
-      <c r="G86" s="10" t="inlineStr">
+      <c r="G105" s="10" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="6" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="6" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B87" s="6" t="inlineStr">
+      <c r="B106" s="6" t="inlineStr">
         <is>
           <t>BIGINT</t>
         </is>
       </c>
-      <c r="C87" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D87" s="6" t="inlineStr"/>
-      <c r="E87" s="6" t="inlineStr">
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D106" s="6" t="inlineStr"/>
+      <c r="E106" s="6" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="F87" s="6" t="inlineStr">
+      <c r="F106" s="6" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="G87" s="6" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="5" t="inlineStr">
+      <c r="G106" s="6" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="5" t="inlineStr">
         <is>
           <t>award_id</t>
         </is>
       </c>
-      <c r="B88" s="5" t="inlineStr">
+      <c r="B107" s="5" t="inlineStr">
         <is>
           <t>VARCHAR(100)</t>
         </is>
       </c>
-      <c r="C88" s="5" t="inlineStr">
+      <c r="C107" s="5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="D88" s="5" t="inlineStr"/>
-      <c r="E88" s="5" t="inlineStr"/>
-      <c r="F88" s="5" t="inlineStr">
+      <c r="D107" s="5" t="inlineStr"/>
+      <c r="E107" s="5" t="inlineStr"/>
+      <c r="F107" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="G88" s="5" t="inlineStr">
+      <c r="G107" s="5" t="inlineStr">
         <is>
           <t>FK to usaspending_award</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="6" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="6" t="inlineStr">
         <is>
           <t>action_date</t>
         </is>
       </c>
-      <c r="B89" s="6" t="inlineStr">
+      <c r="B108" s="6" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="C89" s="6" t="inlineStr">
+      <c r="C108" s="6" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="D89" s="6" t="inlineStr"/>
-      <c r="E89" s="6" t="inlineStr"/>
-      <c r="F89" s="6" t="inlineStr">
+      <c r="D108" s="6" t="inlineStr"/>
+      <c r="E108" s="6" t="inlineStr"/>
+      <c r="F108" s="6" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="G89" s="6" t="inlineStr">
+      <c r="G108" s="6" t="inlineStr">
         <is>
           <t>Transaction action date</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="5" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="5" t="inlineStr">
         <is>
           <t>modification_number</t>
         </is>
       </c>
-      <c r="B90" s="5" t="inlineStr">
+      <c r="B109" s="5" t="inlineStr">
         <is>
           <t>VARCHAR(25)</t>
         </is>
       </c>
-      <c r="C90" s="5" t="inlineStr">
+      <c r="C109" s="5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="D90" s="5" t="inlineStr"/>
-      <c r="E90" s="5" t="inlineStr"/>
-      <c r="F90" s="5" t="inlineStr">
+      <c r="D109" s="5" t="inlineStr"/>
+      <c r="E109" s="5" t="inlineStr"/>
+      <c r="F109" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="G90" s="5" t="inlineStr">
+      <c r="G109" s="5" t="inlineStr">
         <is>
           <t>Contract modification sequence number</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="6" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="6" t="inlineStr">
         <is>
           <t>action_type</t>
         </is>
       </c>
-      <c r="B91" s="6" t="inlineStr">
+      <c r="B110" s="6" t="inlineStr">
         <is>
           <t>VARCHAR(5)</t>
         </is>
       </c>
-      <c r="C91" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D91" s="6" t="inlineStr"/>
-      <c r="E91" s="6" t="inlineStr"/>
-      <c r="F91" s="6" t="inlineStr"/>
-      <c r="G91" s="6" t="inlineStr">
+      <c r="C110" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D110" s="6" t="inlineStr"/>
+      <c r="E110" s="6" t="inlineStr"/>
+      <c r="F110" s="6" t="inlineStr"/>
+      <c r="G110" s="6" t="inlineStr">
         <is>
           <t>Transaction action type code</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="5" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="5" t="inlineStr">
         <is>
           <t>action_type_description</t>
         </is>
       </c>
-      <c r="B92" s="5" t="inlineStr">
+      <c r="B111" s="5" t="inlineStr">
         <is>
           <t>VARCHAR(100)</t>
         </is>
       </c>
-      <c r="C92" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D92" s="5" t="inlineStr"/>
-      <c r="E92" s="5" t="inlineStr"/>
-      <c r="F92" s="5" t="inlineStr"/>
-      <c r="G92" s="5" t="inlineStr">
+      <c r="C111" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D111" s="5" t="inlineStr"/>
+      <c r="E111" s="5" t="inlineStr"/>
+      <c r="F111" s="5" t="inlineStr"/>
+      <c r="G111" s="5" t="inlineStr">
         <is>
           <t>Transaction action type description</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="6" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="6" t="inlineStr">
         <is>
           <t>federal_action_obligation</t>
         </is>
       </c>
-      <c r="B93" s="6" t="inlineStr">
+      <c r="B112" s="6" t="inlineStr">
         <is>
           <t>DECIMAL(15</t>
         </is>
       </c>
-      <c r="C93" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D93" s="6" t="inlineStr"/>
-      <c r="E93" s="6" t="inlineStr"/>
-      <c r="F93" s="6" t="inlineStr"/>
-      <c r="G93" s="6" t="inlineStr">
+      <c r="C112" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D112" s="6" t="inlineStr"/>
+      <c r="E112" s="6" t="inlineStr"/>
+      <c r="F112" s="6" t="inlineStr"/>
+      <c r="G112" s="6" t="inlineStr">
         <is>
           <t>Transaction obligation amount</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="5" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="5" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="B94" s="5" t="inlineStr">
+      <c r="B113" s="5" t="inlineStr">
         <is>
           <t>TEXT</t>
         </is>
       </c>
-      <c r="C94" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D94" s="5" t="inlineStr"/>
-      <c r="E94" s="5" t="inlineStr"/>
-      <c r="F94" s="5" t="inlineStr"/>
-      <c r="G94" s="5" t="inlineStr">
+      <c r="C113" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D113" s="5" t="inlineStr"/>
+      <c r="E113" s="5" t="inlineStr"/>
+      <c r="F113" s="5" t="inlineStr"/>
+      <c r="G113" s="5" t="inlineStr">
         <is>
           <t>Description text</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="6" t="inlineStr">
-        <is>
-          <t>first_loaded_at</t>
-        </is>
-      </c>
-      <c r="B95" s="6" t="inlineStr">
-        <is>
-          <t>DATETIME</t>
-        </is>
-      </c>
-      <c r="C95" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D95" s="6" t="inlineStr">
-        <is>
-          <t>CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="E95" s="6" t="inlineStr"/>
-      <c r="F95" s="6" t="inlineStr"/>
-      <c r="G95" s="6" t="inlineStr">
-        <is>
-          <t>Timestamp of initial ETL load</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="5" t="inlineStr">
-        <is>
-          <t>last_load_id</t>
-        </is>
-      </c>
-      <c r="B96" s="5" t="inlineStr">
-        <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="C96" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D96" s="5" t="inlineStr"/>
-      <c r="E96" s="5" t="inlineStr"/>
-      <c r="F96" s="5" t="inlineStr"/>
-      <c r="G96" s="5" t="inlineStr">
-        <is>
-          <t>FK to etl_load_log for traceability</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="6" t="inlineStr">
-        <is>
-          <t>REFERENCES</t>
-        </is>
-      </c>
-      <c r="B97" s="6" t="inlineStr">
-        <is>
-          <t>USASPENDING_AWARD(GENERATED_UNIQUE_AWARD_ID)</t>
-        </is>
-      </c>
-      <c r="C97" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D97" s="6" t="inlineStr"/>
-      <c r="E97" s="6" t="inlineStr"/>
-      <c r="F97" s="6" t="inlineStr"/>
-      <c r="G97" s="6" t="inlineStr"/>
-    </row>
-    <row r="98"/>
-    <row r="99">
-      <c r="A99" s="8" t="inlineStr">
-        <is>
-          <t>usaspending_load_checkpoint</t>
-        </is>
-      </c>
-      <c r="B99" s="9" t="n"/>
-      <c r="C99" s="9" t="n"/>
-      <c r="D99" s="9" t="n"/>
-      <c r="E99" s="9" t="n"/>
-      <c r="F99" s="9" t="n"/>
-      <c r="G99" s="9" t="n"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="10" t="inlineStr">
-        <is>
-          <t>Column Name</t>
-        </is>
-      </c>
-      <c r="B100" s="10" t="inlineStr">
-        <is>
-          <t>Data Type</t>
-        </is>
-      </c>
-      <c r="C100" s="10" t="inlineStr">
-        <is>
-          <t>Nullable</t>
-        </is>
-      </c>
-      <c r="D100" s="10" t="inlineStr">
-        <is>
-          <t>Default</t>
-        </is>
-      </c>
-      <c r="E100" s="10" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="F100" s="10" t="inlineStr">
-        <is>
-          <t>Index</t>
-        </is>
-      </c>
-      <c r="G100" s="10" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="6" t="inlineStr">
-        <is>
-          <t>checkpoint_id</t>
-        </is>
-      </c>
-      <c r="B101" s="6" t="inlineStr">
-        <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="C101" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D101" s="6" t="inlineStr"/>
-      <c r="E101" s="6" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="F101" s="6" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G101" s="6" t="inlineStr">
-        <is>
-          <t>Auto-increment checkpoint ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="5" t="inlineStr">
-        <is>
-          <t>load_id</t>
-        </is>
-      </c>
-      <c r="B102" s="5" t="inlineStr">
-        <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="C102" s="5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D102" s="5" t="inlineStr"/>
-      <c r="E102" s="5" t="inlineStr"/>
-      <c r="F102" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G102" s="5" t="inlineStr">
-        <is>
-          <t>FK to etl_load_log</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="6" t="inlineStr">
-        <is>
-          <t>fiscal_year</t>
-        </is>
-      </c>
-      <c r="B103" s="6" t="inlineStr">
-        <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="C103" s="6" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D103" s="6" t="inlineStr"/>
-      <c r="E103" s="6" t="inlineStr"/>
-      <c r="F103" s="6" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G103" s="6" t="inlineStr">
-        <is>
-          <t>Federal fiscal year</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="5" t="inlineStr">
-        <is>
-          <t>csv_file_name</t>
-        </is>
-      </c>
-      <c r="B104" s="5" t="inlineStr">
-        <is>
-          <t>VARCHAR(255)</t>
-        </is>
-      </c>
-      <c r="C104" s="5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D104" s="5" t="inlineStr"/>
-      <c r="E104" s="5" t="inlineStr"/>
-      <c r="F104" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G104" s="5" t="inlineStr">
-        <is>
-          <t>Name of CSV file being loaded</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B105" s="6" t="inlineStr">
-        <is>
-          <t>ENUM(</t>
-        </is>
-      </c>
-      <c r="C105" s="6" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D105" s="6" t="inlineStr">
-        <is>
-          <t>IN_PROGRESS</t>
-        </is>
-      </c>
-      <c r="E105" s="6" t="inlineStr"/>
-      <c r="F105" s="6" t="inlineStr"/>
-      <c r="G105" s="6" t="inlineStr">
-        <is>
-          <t>Organization status</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="5" t="inlineStr">
-        <is>
-          <t>completed_batches</t>
-        </is>
-      </c>
-      <c r="B106" s="5" t="inlineStr">
-        <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="C106" s="5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D106" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E106" s="5" t="inlineStr"/>
-      <c r="F106" s="5" t="inlineStr"/>
-      <c r="G106" s="5" t="inlineStr">
-        <is>
-          <t>Number of batches completed</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="6" t="inlineStr">
-        <is>
-          <t>total_rows_loaded</t>
-        </is>
-      </c>
-      <c r="B107" s="6" t="inlineStr">
-        <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="C107" s="6" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D107" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E107" s="6" t="inlineStr"/>
-      <c r="F107" s="6" t="inlineStr"/>
-      <c r="G107" s="6" t="inlineStr">
-        <is>
-          <t>Total rows loaded so far</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="5" t="inlineStr">
-        <is>
-          <t>archive_hash</t>
-        </is>
-      </c>
-      <c r="B108" s="5" t="inlineStr">
-        <is>
-          <t>VARCHAR(130)</t>
-        </is>
-      </c>
-      <c r="C108" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D108" s="5" t="inlineStr"/>
-      <c r="E108" s="5" t="inlineStr"/>
-      <c r="F108" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G108" s="5" t="inlineStr">
-        <is>
-          <t>SHA-256 hash (first 1MB) + file size for FY dedup</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="6" t="inlineStr">
-        <is>
-          <t>started_at</t>
-        </is>
-      </c>
-      <c r="B109" s="6" t="inlineStr">
-        <is>
-          <t>TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="C109" s="6" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D109" s="6" t="inlineStr">
-        <is>
-          <t>CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="E109" s="6" t="inlineStr"/>
-      <c r="F109" s="6" t="inlineStr"/>
-      <c r="G109" s="6" t="inlineStr">
-        <is>
-          <t>Load start timestamp</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="5" t="inlineStr">
-        <is>
-          <t>completed_at</t>
-        </is>
-      </c>
-      <c r="B110" s="5" t="inlineStr">
-        <is>
-          <t>TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="C110" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D110" s="5" t="inlineStr"/>
-      <c r="E110" s="5" t="inlineStr"/>
-      <c r="F110" s="5" t="inlineStr"/>
-      <c r="G110" s="5" t="inlineStr">
-        <is>
-          <t>Load completion timestamp</t>
-        </is>
-      </c>
-    </row>
-    <row r="111"/>
-    <row r="112">
-      <c r="A112" s="8" t="inlineStr">
-        <is>
-          <t>sam_subaward</t>
-        </is>
-      </c>
-      <c r="B112" s="9" t="n"/>
-      <c r="C112" s="9" t="n"/>
-      <c r="D112" s="9" t="n"/>
-      <c r="E112" s="9" t="n"/>
-      <c r="F112" s="9" t="n"/>
-      <c r="G112" s="9" t="n"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="10" t="inlineStr">
-        <is>
-          <t>Column Name</t>
-        </is>
-      </c>
-      <c r="B113" s="10" t="inlineStr">
-        <is>
-          <t>Data Type</t>
-        </is>
-      </c>
-      <c r="C113" s="10" t="inlineStr">
-        <is>
-          <t>Nullable</t>
-        </is>
-      </c>
-      <c r="D113" s="10" t="inlineStr">
-        <is>
-          <t>Default</t>
-        </is>
-      </c>
-      <c r="E113" s="10" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="F113" s="10" t="inlineStr">
-        <is>
-          <t>Index</t>
-        </is>
-      </c>
-      <c r="G113" s="10" t="inlineStr">
-        <is>
-          <t>Description</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="6" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>first_loaded_at</t>
         </is>
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>INT</t>
+          <t>DATETIME</t>
         </is>
       </c>
       <c r="C114" s="6" t="inlineStr">
@@ -7597,28 +6200,28 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="D114" s="6" t="inlineStr"/>
-      <c r="E114" s="6" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="F114" s="6" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G114" s="6" t="inlineStr"/>
+      <c r="D114" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="E114" s="6" t="inlineStr"/>
+      <c r="F114" s="6" t="inlineStr"/>
+      <c r="G114" s="6" t="inlineStr">
+        <is>
+          <t>Timestamp of initial ETL load</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>prime_piid</t>
+          <t>last_load_id</t>
         </is>
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>VARCHAR(50)</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
@@ -7628,26 +6231,22 @@
       </c>
       <c r="D115" s="5" t="inlineStr"/>
       <c r="E115" s="5" t="inlineStr"/>
-      <c r="F115" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="F115" s="5" t="inlineStr"/>
       <c r="G115" s="5" t="inlineStr">
         <is>
-          <t>Prime contract PIID</t>
+          <t>FK to etl_load_log for traceability</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="6" t="inlineStr">
         <is>
-          <t>prime_agency_id</t>
+          <t>REFERENCES</t>
         </is>
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>VARCHAR(10)</t>
+          <t>USASPENDING_AWARD(GENERATED_UNIQUE_AWARD_ID)</t>
         </is>
       </c>
       <c r="C116" s="6" t="inlineStr">
@@ -7658,100 +6257,68 @@
       <c r="D116" s="6" t="inlineStr"/>
       <c r="E116" s="6" t="inlineStr"/>
       <c r="F116" s="6" t="inlineStr"/>
-      <c r="G116" s="6" t="inlineStr">
-        <is>
-          <t>Prime contract agency code</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="5" t="inlineStr">
-        <is>
-          <t>prime_agency_name</t>
-        </is>
-      </c>
-      <c r="B117" s="5" t="inlineStr">
-        <is>
-          <t>VARCHAR(200)</t>
-        </is>
-      </c>
-      <c r="C117" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D117" s="5" t="inlineStr"/>
-      <c r="E117" s="5" t="inlineStr"/>
-      <c r="F117" s="5" t="inlineStr"/>
-      <c r="G117" s="5" t="inlineStr">
-        <is>
-          <t>Prime contract agency name</t>
-        </is>
-      </c>
-    </row>
+      <c r="G116" s="6" t="inlineStr"/>
+    </row>
+    <row r="117"/>
     <row r="118">
-      <c r="A118" s="6" t="inlineStr">
-        <is>
-          <t>prime_uei</t>
-        </is>
-      </c>
-      <c r="B118" s="6" t="inlineStr">
-        <is>
-          <t>VARCHAR(12)</t>
-        </is>
-      </c>
-      <c r="C118" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D118" s="6" t="inlineStr"/>
-      <c r="E118" s="6" t="inlineStr"/>
-      <c r="F118" s="6" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G118" s="6" t="inlineStr">
-        <is>
-          <t>Prime contractor UEI</t>
-        </is>
-      </c>
+      <c r="A118" s="8" t="inlineStr">
+        <is>
+          <t>usaspending_load_checkpoint</t>
+        </is>
+      </c>
+      <c r="B118" s="9" t="n"/>
+      <c r="C118" s="9" t="n"/>
+      <c r="D118" s="9" t="n"/>
+      <c r="E118" s="9" t="n"/>
+      <c r="F118" s="9" t="n"/>
+      <c r="G118" s="9" t="n"/>
     </row>
     <row r="119">
-      <c r="A119" s="5" t="inlineStr">
-        <is>
-          <t>prime_name</t>
-        </is>
-      </c>
-      <c r="B119" s="5" t="inlineStr">
-        <is>
-          <t>VARCHAR(500)</t>
-        </is>
-      </c>
-      <c r="C119" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D119" s="5" t="inlineStr"/>
-      <c r="E119" s="5" t="inlineStr"/>
-      <c r="F119" s="5" t="inlineStr"/>
-      <c r="G119" s="5" t="inlineStr">
-        <is>
-          <t>Prime contractor name</t>
+      <c r="A119" s="10" t="inlineStr">
+        <is>
+          <t>Column Name</t>
+        </is>
+      </c>
+      <c r="B119" s="10" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="C119" s="10" t="inlineStr">
+        <is>
+          <t>Nullable</t>
+        </is>
+      </c>
+      <c r="D119" s="10" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="E119" s="10" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="F119" s="10" t="inlineStr">
+        <is>
+          <t>Index</t>
+        </is>
+      </c>
+      <c r="G119" s="10" t="inlineStr">
+        <is>
+          <t>Description</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="6" t="inlineStr">
         <is>
-          <t>sub_uei</t>
+          <t>checkpoint_id</t>
         </is>
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>VARCHAR(12)</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="C120" s="6" t="inlineStr">
@@ -7760,7 +6327,11 @@
         </is>
       </c>
       <c r="D120" s="6" t="inlineStr"/>
-      <c r="E120" s="6" t="inlineStr"/>
+      <c r="E120" s="6" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="F120" s="6" t="inlineStr">
         <is>
           <t>Y</t>
@@ -7768,74 +6339,82 @@
       </c>
       <c r="G120" s="6" t="inlineStr">
         <is>
-          <t>Subcontractor UEI</t>
+          <t>Auto-increment checkpoint ID</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>sub_name</t>
+          <t>load_id</t>
         </is>
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>VARCHAR(500)</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr"/>
       <c r="E121" s="5" t="inlineStr"/>
-      <c r="F121" s="5" t="inlineStr"/>
+      <c r="F121" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="G121" s="5" t="inlineStr">
         <is>
-          <t>Subcontractor name</t>
+          <t>FK to etl_load_log</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="6" t="inlineStr">
         <is>
-          <t>sub_amount</t>
+          <t>fiscal_year</t>
         </is>
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>DECIMAL(15</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="C122" s="6" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="D122" s="6" t="inlineStr"/>
       <c r="E122" s="6" t="inlineStr"/>
-      <c r="F122" s="6" t="inlineStr"/>
+      <c r="F122" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="G122" s="6" t="inlineStr">
         <is>
-          <t>Subaward dollar amount</t>
+          <t>Federal fiscal year</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>sub_date</t>
+          <t>csv_file_name</t>
         </is>
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>DATE</t>
+          <t>VARCHAR(255)</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr"/>
@@ -7847,98 +6426,106 @@
       </c>
       <c r="G123" s="5" t="inlineStr">
         <is>
-          <t>Subaward date</t>
+          <t>Name of CSV file being loaded</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="6" t="inlineStr">
         <is>
-          <t>sub_description</t>
+          <t>status</t>
         </is>
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>ENUM(</t>
         </is>
       </c>
       <c r="C124" s="6" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D124" s="6" t="inlineStr"/>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D124" s="6" t="inlineStr">
+        <is>
+          <t>IN_PROGRESS</t>
+        </is>
+      </c>
       <c r="E124" s="6" t="inlineStr"/>
       <c r="F124" s="6" t="inlineStr"/>
       <c r="G124" s="6" t="inlineStr">
         <is>
-          <t>Subaward description</t>
+          <t>Organization status</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>naics_code</t>
+          <t>completed_batches</t>
         </is>
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>VARCHAR(6)</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D125" s="5" t="inlineStr"/>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D125" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="E125" s="5" t="inlineStr"/>
-      <c r="F125" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="F125" s="5" t="inlineStr"/>
       <c r="G125" s="5" t="inlineStr">
         <is>
-          <t>NAICS industry classification code</t>
+          <t>Number of batches completed</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="6" t="inlineStr">
         <is>
-          <t>psc_code</t>
+          <t>total_rows_loaded</t>
         </is>
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>VARCHAR(10)</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="C126" s="6" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D126" s="6" t="inlineStr"/>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D126" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="E126" s="6" t="inlineStr"/>
       <c r="F126" s="6" t="inlineStr"/>
       <c r="G126" s="6" t="inlineStr">
         <is>
-          <t>Product/Service Code</t>
+          <t>Total rows loaded so far</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>sub_business_type</t>
+          <t>archive_hash</t>
         </is>
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>VARCHAR(50)</t>
+          <t>VARCHAR(130)</t>
         </is>
       </c>
       <c r="C127" s="5" t="inlineStr">
@@ -7948,47 +6535,55 @@
       </c>
       <c r="D127" s="5" t="inlineStr"/>
       <c r="E127" s="5" t="inlineStr"/>
-      <c r="F127" s="5" t="inlineStr"/>
+      <c r="F127" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="G127" s="5" t="inlineStr">
         <is>
-          <t>Subcontractor business type codes</t>
+          <t>SHA-256 hash (first 1MB) + file size for FY dedup</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="6" t="inlineStr">
         <is>
-          <t>pop_state</t>
+          <t>started_at</t>
         </is>
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>VARCHAR(100)</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="C128" s="6" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D128" s="6" t="inlineStr"/>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D128" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
       <c r="E128" s="6" t="inlineStr"/>
       <c r="F128" s="6" t="inlineStr"/>
       <c r="G128" s="6" t="inlineStr">
         <is>
-          <t>Place of performance state (ISO 3166-2)</t>
+          <t>Load start timestamp</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>pop_country</t>
+          <t>completed_at</t>
         </is>
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>VARCHAR(3)</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
@@ -8001,786 +6596,1262 @@
       <c r="F129" s="5" t="inlineStr"/>
       <c r="G129" s="5" t="inlineStr">
         <is>
+          <t>Load completion timestamp</t>
+        </is>
+      </c>
+    </row>
+    <row r="130"/>
+    <row r="131">
+      <c r="A131" s="8" t="inlineStr">
+        <is>
+          <t>sam_subaward</t>
+        </is>
+      </c>
+      <c r="B131" s="9" t="n"/>
+      <c r="C131" s="9" t="n"/>
+      <c r="D131" s="9" t="n"/>
+      <c r="E131" s="9" t="n"/>
+      <c r="F131" s="9" t="n"/>
+      <c r="G131" s="9" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="10" t="inlineStr">
+        <is>
+          <t>Column Name</t>
+        </is>
+      </c>
+      <c r="B132" s="10" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="C132" s="10" t="inlineStr">
+        <is>
+          <t>Nullable</t>
+        </is>
+      </c>
+      <c r="D132" s="10" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="E132" s="10" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="F132" s="10" t="inlineStr">
+        <is>
+          <t>Index</t>
+        </is>
+      </c>
+      <c r="G132" s="10" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="6" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B133" s="6" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="C133" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D133" s="6" t="inlineStr"/>
+      <c r="E133" s="6" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="F133" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G133" s="6" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="5" t="inlineStr">
+        <is>
+          <t>prime_piid</t>
+        </is>
+      </c>
+      <c r="B134" s="5" t="inlineStr">
+        <is>
+          <t>VARCHAR(50)</t>
+        </is>
+      </c>
+      <c r="C134" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D134" s="5" t="inlineStr"/>
+      <c r="E134" s="5" t="inlineStr"/>
+      <c r="F134" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G134" s="5" t="inlineStr">
+        <is>
+          <t>Prime contract PIID</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="6" t="inlineStr">
+        <is>
+          <t>prime_agency_id</t>
+        </is>
+      </c>
+      <c r="B135" s="6" t="inlineStr">
+        <is>
+          <t>VARCHAR(10)</t>
+        </is>
+      </c>
+      <c r="C135" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D135" s="6" t="inlineStr"/>
+      <c r="E135" s="6" t="inlineStr"/>
+      <c r="F135" s="6" t="inlineStr"/>
+      <c r="G135" s="6" t="inlineStr">
+        <is>
+          <t>Prime contract agency code</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="5" t="inlineStr">
+        <is>
+          <t>prime_agency_name</t>
+        </is>
+      </c>
+      <c r="B136" s="5" t="inlineStr">
+        <is>
+          <t>VARCHAR(200)</t>
+        </is>
+      </c>
+      <c r="C136" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D136" s="5" t="inlineStr"/>
+      <c r="E136" s="5" t="inlineStr"/>
+      <c r="F136" s="5" t="inlineStr"/>
+      <c r="G136" s="5" t="inlineStr">
+        <is>
+          <t>Prime contract agency name</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="6" t="inlineStr">
+        <is>
+          <t>prime_uei</t>
+        </is>
+      </c>
+      <c r="B137" s="6" t="inlineStr">
+        <is>
+          <t>VARCHAR(12)</t>
+        </is>
+      </c>
+      <c r="C137" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D137" s="6" t="inlineStr"/>
+      <c r="E137" s="6" t="inlineStr"/>
+      <c r="F137" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G137" s="6" t="inlineStr">
+        <is>
+          <t>Prime contractor UEI</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="5" t="inlineStr">
+        <is>
+          <t>prime_name</t>
+        </is>
+      </c>
+      <c r="B138" s="5" t="inlineStr">
+        <is>
+          <t>VARCHAR(500)</t>
+        </is>
+      </c>
+      <c r="C138" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D138" s="5" t="inlineStr"/>
+      <c r="E138" s="5" t="inlineStr"/>
+      <c r="F138" s="5" t="inlineStr"/>
+      <c r="G138" s="5" t="inlineStr">
+        <is>
+          <t>Prime contractor name</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="6" t="inlineStr">
+        <is>
+          <t>sub_uei</t>
+        </is>
+      </c>
+      <c r="B139" s="6" t="inlineStr">
+        <is>
+          <t>VARCHAR(12)</t>
+        </is>
+      </c>
+      <c r="C139" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D139" s="6" t="inlineStr"/>
+      <c r="E139" s="6" t="inlineStr"/>
+      <c r="F139" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G139" s="6" t="inlineStr">
+        <is>
+          <t>Subcontractor UEI</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="5" t="inlineStr">
+        <is>
+          <t>sub_name</t>
+        </is>
+      </c>
+      <c r="B140" s="5" t="inlineStr">
+        <is>
+          <t>VARCHAR(500)</t>
+        </is>
+      </c>
+      <c r="C140" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D140" s="5" t="inlineStr"/>
+      <c r="E140" s="5" t="inlineStr"/>
+      <c r="F140" s="5" t="inlineStr"/>
+      <c r="G140" s="5" t="inlineStr">
+        <is>
+          <t>Subcontractor name</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="6" t="inlineStr">
+        <is>
+          <t>sub_amount</t>
+        </is>
+      </c>
+      <c r="B141" s="6" t="inlineStr">
+        <is>
+          <t>DECIMAL(15</t>
+        </is>
+      </c>
+      <c r="C141" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D141" s="6" t="inlineStr"/>
+      <c r="E141" s="6" t="inlineStr"/>
+      <c r="F141" s="6" t="inlineStr"/>
+      <c r="G141" s="6" t="inlineStr">
+        <is>
+          <t>Subaward dollar amount</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="5" t="inlineStr">
+        <is>
+          <t>sub_date</t>
+        </is>
+      </c>
+      <c r="B142" s="5" t="inlineStr">
+        <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="C142" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D142" s="5" t="inlineStr"/>
+      <c r="E142" s="5" t="inlineStr"/>
+      <c r="F142" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G142" s="5" t="inlineStr">
+        <is>
+          <t>Subaward date</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="6" t="inlineStr">
+        <is>
+          <t>sub_description</t>
+        </is>
+      </c>
+      <c r="B143" s="6" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="C143" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D143" s="6" t="inlineStr"/>
+      <c r="E143" s="6" t="inlineStr"/>
+      <c r="F143" s="6" t="inlineStr"/>
+      <c r="G143" s="6" t="inlineStr">
+        <is>
+          <t>Subaward description</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="5" t="inlineStr">
+        <is>
+          <t>naics_code</t>
+        </is>
+      </c>
+      <c r="B144" s="5" t="inlineStr">
+        <is>
+          <t>VARCHAR(6)</t>
+        </is>
+      </c>
+      <c r="C144" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D144" s="5" t="inlineStr"/>
+      <c r="E144" s="5" t="inlineStr"/>
+      <c r="F144" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G144" s="5" t="inlineStr">
+        <is>
+          <t>NAICS industry classification code</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="6" t="inlineStr">
+        <is>
+          <t>psc_code</t>
+        </is>
+      </c>
+      <c r="B145" s="6" t="inlineStr">
+        <is>
+          <t>VARCHAR(10)</t>
+        </is>
+      </c>
+      <c r="C145" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D145" s="6" t="inlineStr"/>
+      <c r="E145" s="6" t="inlineStr"/>
+      <c r="F145" s="6" t="inlineStr"/>
+      <c r="G145" s="6" t="inlineStr">
+        <is>
+          <t>Product/Service Code</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="5" t="inlineStr">
+        <is>
+          <t>sub_business_type</t>
+        </is>
+      </c>
+      <c r="B146" s="5" t="inlineStr">
+        <is>
+          <t>VARCHAR(50)</t>
+        </is>
+      </c>
+      <c r="C146" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D146" s="5" t="inlineStr"/>
+      <c r="E146" s="5" t="inlineStr"/>
+      <c r="F146" s="5" t="inlineStr"/>
+      <c r="G146" s="5" t="inlineStr">
+        <is>
+          <t>Subcontractor business type codes</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="6" t="inlineStr">
+        <is>
+          <t>pop_state</t>
+        </is>
+      </c>
+      <c r="B147" s="6" t="inlineStr">
+        <is>
+          <t>VARCHAR(100)</t>
+        </is>
+      </c>
+      <c r="C147" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D147" s="6" t="inlineStr"/>
+      <c r="E147" s="6" t="inlineStr"/>
+      <c r="F147" s="6" t="inlineStr"/>
+      <c r="G147" s="6" t="inlineStr">
+        <is>
+          <t>Place of performance state (ISO 3166-2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="5" t="inlineStr">
+        <is>
+          <t>pop_country</t>
+        </is>
+      </c>
+      <c r="B148" s="5" t="inlineStr">
+        <is>
+          <t>VARCHAR(3)</t>
+        </is>
+      </c>
+      <c r="C148" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D148" s="5" t="inlineStr"/>
+      <c r="E148" s="5" t="inlineStr"/>
+      <c r="F148" s="5" t="inlineStr"/>
+      <c r="G148" s="5" t="inlineStr">
+        <is>
           <t>Place of performance country code</t>
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="6" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="6" t="inlineStr">
         <is>
           <t>pop_zip</t>
         </is>
       </c>
-      <c r="B130" s="6" t="inlineStr">
+      <c r="B149" s="6" t="inlineStr">
         <is>
           <t>VARCHAR(10)</t>
         </is>
       </c>
-      <c r="C130" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D130" s="6" t="inlineStr"/>
-      <c r="E130" s="6" t="inlineStr"/>
-      <c r="F130" s="6" t="inlineStr"/>
-      <c r="G130" s="6" t="inlineStr">
+      <c r="C149" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D149" s="6" t="inlineStr"/>
+      <c r="E149" s="6" t="inlineStr"/>
+      <c r="F149" s="6" t="inlineStr"/>
+      <c r="G149" s="6" t="inlineStr">
         <is>
           <t>Place of performance ZIP code</t>
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="5" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="5" t="inlineStr">
         <is>
           <t>recovery_model_q1</t>
         </is>
       </c>
-      <c r="B131" s="5" t="inlineStr">
+      <c r="B150" s="5" t="inlineStr">
         <is>
           <t>VARCHAR(3)</t>
         </is>
       </c>
-      <c r="C131" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D131" s="5" t="inlineStr"/>
-      <c r="E131" s="5" t="inlineStr"/>
-      <c r="F131" s="5" t="inlineStr"/>
-      <c r="G131" s="5" t="inlineStr">
+      <c r="C150" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D150" s="5" t="inlineStr"/>
+      <c r="E150" s="5" t="inlineStr"/>
+      <c r="F150" s="5" t="inlineStr"/>
+      <c r="G150" s="5" t="inlineStr">
         <is>
           <t>Y/N recovery act</t>
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="6" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="6" t="inlineStr">
         <is>
           <t>recovery_model_q2</t>
         </is>
       </c>
-      <c r="B132" s="6" t="inlineStr">
+      <c r="B151" s="6" t="inlineStr">
         <is>
           <t>VARCHAR(3)</t>
         </is>
       </c>
-      <c r="C132" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D132" s="6" t="inlineStr"/>
-      <c r="E132" s="6" t="inlineStr"/>
-      <c r="F132" s="6" t="inlineStr"/>
-      <c r="G132" s="6" t="inlineStr"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="5" t="inlineStr">
+      <c r="C151" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D151" s="6" t="inlineStr"/>
+      <c r="E151" s="6" t="inlineStr"/>
+      <c r="F151" s="6" t="inlineStr"/>
+      <c r="G151" s="6" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="5" t="inlineStr">
         <is>
           <t>record_hash</t>
         </is>
       </c>
-      <c r="B133" s="5" t="inlineStr">
+      <c r="B152" s="5" t="inlineStr">
         <is>
           <t>CHAR(64)</t>
         </is>
       </c>
-      <c r="C133" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D133" s="5" t="inlineStr"/>
-      <c r="E133" s="5" t="inlineStr"/>
-      <c r="F133" s="5" t="inlineStr">
+      <c r="C152" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D152" s="5" t="inlineStr"/>
+      <c r="E152" s="5" t="inlineStr"/>
+      <c r="F152" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="G133" s="5" t="inlineStr">
+      <c r="G152" s="5" t="inlineStr">
         <is>
           <t>SHA-256 hash for change detection</t>
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="6" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="6" t="inlineStr">
         <is>
           <t>first_loaded_at</t>
         </is>
       </c>
-      <c r="B134" s="6" t="inlineStr">
+      <c r="B153" s="6" t="inlineStr">
         <is>
           <t>DATETIME</t>
         </is>
       </c>
-      <c r="C134" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D134" s="6" t="inlineStr">
+      <c r="C153" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D153" s="6" t="inlineStr">
         <is>
           <t>CURRENT_TIMESTAMP</t>
         </is>
       </c>
-      <c r="E134" s="6" t="inlineStr"/>
-      <c r="F134" s="6" t="inlineStr"/>
-      <c r="G134" s="6" t="inlineStr">
+      <c r="E153" s="6" t="inlineStr"/>
+      <c r="F153" s="6" t="inlineStr"/>
+      <c r="G153" s="6" t="inlineStr">
         <is>
           <t>Timestamp of initial ETL load</t>
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="5" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="5" t="inlineStr">
         <is>
           <t>last_updated_at</t>
         </is>
       </c>
-      <c r="B135" s="5" t="inlineStr">
+      <c r="B154" s="5" t="inlineStr">
         <is>
           <t>DATETIME</t>
         </is>
       </c>
-      <c r="C135" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D135" s="5" t="inlineStr">
+      <c r="C154" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D154" s="5" t="inlineStr">
         <is>
           <t>CURRENT_TIMESTAMP</t>
         </is>
       </c>
-      <c r="E135" s="5" t="inlineStr"/>
-      <c r="F135" s="5" t="inlineStr"/>
-      <c r="G135" s="5" t="inlineStr"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="6" t="inlineStr">
+      <c r="E154" s="5" t="inlineStr"/>
+      <c r="F154" s="5" t="inlineStr"/>
+      <c r="G154" s="5" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="6" t="inlineStr">
         <is>
           <t>last_load_id</t>
         </is>
       </c>
-      <c r="B136" s="6" t="inlineStr">
+      <c r="B155" s="6" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="C136" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D136" s="6" t="inlineStr"/>
-      <c r="E136" s="6" t="inlineStr"/>
-      <c r="F136" s="6" t="inlineStr"/>
-      <c r="G136" s="6" t="inlineStr">
+      <c r="C155" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D155" s="6" t="inlineStr"/>
+      <c r="E155" s="6" t="inlineStr"/>
+      <c r="F155" s="6" t="inlineStr"/>
+      <c r="G155" s="6" t="inlineStr">
         <is>
           <t>FK to etl_load_log for traceability</t>
         </is>
       </c>
     </row>
-    <row r="137"/>
-    <row r="138">
-      <c r="A138" s="8" t="inlineStr">
+    <row r="156"/>
+    <row r="157">
+      <c r="A157" s="8" t="inlineStr">
         <is>
           <t>gsa_labor_rate</t>
         </is>
       </c>
-      <c r="B138" s="9" t="n"/>
-      <c r="C138" s="9" t="n"/>
-      <c r="D138" s="9" t="n"/>
-      <c r="E138" s="9" t="n"/>
-      <c r="F138" s="9" t="n"/>
-      <c r="G138" s="9" t="n"/>
-    </row>
-    <row r="139">
-      <c r="A139" s="10" t="inlineStr">
+      <c r="B157" s="9" t="n"/>
+      <c r="C157" s="9" t="n"/>
+      <c r="D157" s="9" t="n"/>
+      <c r="E157" s="9" t="n"/>
+      <c r="F157" s="9" t="n"/>
+      <c r="G157" s="9" t="n"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="10" t="inlineStr">
         <is>
           <t>Column Name</t>
         </is>
       </c>
-      <c r="B139" s="10" t="inlineStr">
+      <c r="B158" s="10" t="inlineStr">
         <is>
           <t>Data Type</t>
         </is>
       </c>
-      <c r="C139" s="10" t="inlineStr">
+      <c r="C158" s="10" t="inlineStr">
         <is>
           <t>Nullable</t>
         </is>
       </c>
-      <c r="D139" s="10" t="inlineStr">
+      <c r="D158" s="10" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="E139" s="10" t="inlineStr">
+      <c r="E158" s="10" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="F139" s="10" t="inlineStr">
+      <c r="F158" s="10" t="inlineStr">
         <is>
           <t>Index</t>
         </is>
       </c>
-      <c r="G139" s="10" t="inlineStr">
+      <c r="G158" s="10" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="6" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="6" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B140" s="6" t="inlineStr">
+      <c r="B159" s="6" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="C140" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D140" s="6" t="inlineStr"/>
-      <c r="E140" s="6" t="inlineStr">
+      <c r="C159" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D159" s="6" t="inlineStr"/>
+      <c r="E159" s="6" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="F140" s="6" t="inlineStr">
+      <c r="F159" s="6" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="G140" s="6" t="inlineStr"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="5" t="inlineStr">
+      <c r="G159" s="6" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="5" t="inlineStr">
         <is>
           <t>labor_category</t>
         </is>
       </c>
-      <c r="B141" s="5" t="inlineStr">
+      <c r="B160" s="5" t="inlineStr">
         <is>
           <t>VARCHAR(200)</t>
         </is>
       </c>
-      <c r="C141" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D141" s="5" t="inlineStr"/>
-      <c r="E141" s="5" t="inlineStr"/>
-      <c r="F141" s="5" t="inlineStr">
+      <c r="C160" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D160" s="5" t="inlineStr"/>
+      <c r="E160" s="5" t="inlineStr"/>
+      <c r="F160" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="G141" s="5" t="inlineStr">
+      <c r="G160" s="5" t="inlineStr">
         <is>
           <t>Labor category title</t>
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="6" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="6" t="inlineStr">
         <is>
           <t>education_level</t>
         </is>
       </c>
-      <c r="B142" s="6" t="inlineStr">
+      <c r="B161" s="6" t="inlineStr">
         <is>
           <t>VARCHAR(50)</t>
         </is>
       </c>
-      <c r="C142" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D142" s="6" t="inlineStr"/>
-      <c r="E142" s="6" t="inlineStr"/>
-      <c r="F142" s="6" t="inlineStr"/>
-      <c r="G142" s="6" t="inlineStr">
+      <c r="C161" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D161" s="6" t="inlineStr"/>
+      <c r="E161" s="6" t="inlineStr"/>
+      <c r="F161" s="6" t="inlineStr"/>
+      <c r="G161" s="6" t="inlineStr">
         <is>
           <t>Required education level</t>
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="5" t="inlineStr">
+    <row r="162">
+      <c r="A162" s="5" t="inlineStr">
         <is>
           <t>min_years_experience</t>
         </is>
       </c>
-      <c r="B143" s="5" t="inlineStr">
+      <c r="B162" s="5" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="C143" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D143" s="5" t="inlineStr"/>
-      <c r="E143" s="5" t="inlineStr"/>
-      <c r="F143" s="5" t="inlineStr"/>
-      <c r="G143" s="5" t="inlineStr">
+      <c r="C162" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D162" s="5" t="inlineStr"/>
+      <c r="E162" s="5" t="inlineStr"/>
+      <c r="F162" s="5" t="inlineStr"/>
+      <c r="G162" s="5" t="inlineStr">
         <is>
           <t>Minimum years of experience required</t>
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="6" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="6" t="inlineStr">
         <is>
           <t>current_price</t>
         </is>
       </c>
-      <c r="B144" s="6" t="inlineStr">
+      <c r="B163" s="6" t="inlineStr">
         <is>
           <t>DECIMAL(10</t>
         </is>
       </c>
-      <c r="C144" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D144" s="6" t="inlineStr"/>
-      <c r="E144" s="6" t="inlineStr"/>
-      <c r="F144" s="6" t="inlineStr"/>
-      <c r="G144" s="6" t="inlineStr">
+      <c r="C163" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D163" s="6" t="inlineStr"/>
+      <c r="E163" s="6" t="inlineStr"/>
+      <c r="F163" s="6" t="inlineStr"/>
+      <c r="G163" s="6" t="inlineStr">
         <is>
           <t>Current hourly rate</t>
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="5" t="inlineStr">
+    <row r="164">
+      <c r="A164" s="5" t="inlineStr">
         <is>
           <t>next_year_price</t>
         </is>
       </c>
-      <c r="B145" s="5" t="inlineStr">
+      <c r="B164" s="5" t="inlineStr">
         <is>
           <t>DECIMAL(10</t>
         </is>
       </c>
-      <c r="C145" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D145" s="5" t="inlineStr"/>
-      <c r="E145" s="5" t="inlineStr"/>
-      <c r="F145" s="5" t="inlineStr"/>
-      <c r="G145" s="5" t="inlineStr">
+      <c r="C164" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D164" s="5" t="inlineStr"/>
+      <c r="E164" s="5" t="inlineStr"/>
+      <c r="F164" s="5" t="inlineStr"/>
+      <c r="G164" s="5" t="inlineStr">
         <is>
           <t>Next option year hourly rate</t>
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="6" t="inlineStr">
+    <row r="165">
+      <c r="A165" s="6" t="inlineStr">
         <is>
           <t>second_year_price</t>
         </is>
       </c>
-      <c r="B146" s="6" t="inlineStr">
+      <c r="B165" s="6" t="inlineStr">
         <is>
           <t>DECIMAL(10</t>
         </is>
       </c>
-      <c r="C146" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D146" s="6" t="inlineStr"/>
-      <c r="E146" s="6" t="inlineStr"/>
-      <c r="F146" s="6" t="inlineStr"/>
-      <c r="G146" s="6" t="inlineStr">
+      <c r="C165" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D165" s="6" t="inlineStr"/>
+      <c r="E165" s="6" t="inlineStr"/>
+      <c r="F165" s="6" t="inlineStr"/>
+      <c r="G165" s="6" t="inlineStr">
         <is>
           <t>Second option year hourly rate</t>
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="5" t="inlineStr">
+    <row r="166">
+      <c r="A166" s="5" t="inlineStr">
         <is>
           <t>schedule</t>
         </is>
       </c>
-      <c r="B147" s="5" t="inlineStr">
+      <c r="B166" s="5" t="inlineStr">
         <is>
           <t>VARCHAR(200)</t>
         </is>
       </c>
-      <c r="C147" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D147" s="5" t="inlineStr"/>
-      <c r="E147" s="5" t="inlineStr"/>
-      <c r="F147" s="5" t="inlineStr">
+      <c r="C166" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D166" s="5" t="inlineStr"/>
+      <c r="E166" s="5" t="inlineStr"/>
+      <c r="F166" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="G147" s="5" t="inlineStr">
+      <c r="G166" s="5" t="inlineStr">
         <is>
           <t>GSA schedule name</t>
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="6" t="inlineStr">
+    <row r="167">
+      <c r="A167" s="6" t="inlineStr">
         <is>
           <t>contractor_name</t>
         </is>
       </c>
-      <c r="B148" s="6" t="inlineStr">
+      <c r="B167" s="6" t="inlineStr">
         <is>
           <t>VARCHAR(200)</t>
         </is>
       </c>
-      <c r="C148" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D148" s="6" t="inlineStr"/>
-      <c r="E148" s="6" t="inlineStr"/>
-      <c r="F148" s="6" t="inlineStr"/>
-      <c r="G148" s="6" t="inlineStr">
+      <c r="C167" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D167" s="6" t="inlineStr"/>
+      <c r="E167" s="6" t="inlineStr"/>
+      <c r="F167" s="6" t="inlineStr"/>
+      <c r="G167" s="6" t="inlineStr">
         <is>
           <t>GSA schedule holder name</t>
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="5" t="inlineStr">
+    <row r="168">
+      <c r="A168" s="5" t="inlineStr">
         <is>
           <t>sin</t>
         </is>
       </c>
-      <c r="B149" s="5" t="inlineStr">
+      <c r="B168" s="5" t="inlineStr">
         <is>
           <t>VARCHAR(500)</t>
         </is>
       </c>
-      <c r="C149" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D149" s="5" t="inlineStr"/>
-      <c r="E149" s="5" t="inlineStr"/>
-      <c r="F149" s="5" t="inlineStr"/>
-      <c r="G149" s="5" t="inlineStr">
+      <c r="C168" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D168" s="5" t="inlineStr"/>
+      <c r="E168" s="5" t="inlineStr"/>
+      <c r="F168" s="5" t="inlineStr"/>
+      <c r="G168" s="5" t="inlineStr">
         <is>
           <t>Special Item Number(s)</t>
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="6" t="inlineStr">
+    <row r="169">
+      <c r="A169" s="6" t="inlineStr">
         <is>
           <t>business_size</t>
         </is>
       </c>
-      <c r="B150" s="6" t="inlineStr">
+      <c r="B169" s="6" t="inlineStr">
         <is>
           <t>VARCHAR(10)</t>
         </is>
       </c>
-      <c r="C150" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D150" s="6" t="inlineStr"/>
-      <c r="E150" s="6" t="inlineStr"/>
-      <c r="F150" s="6" t="inlineStr">
+      <c r="C169" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D169" s="6" t="inlineStr"/>
+      <c r="E169" s="6" t="inlineStr"/>
+      <c r="F169" s="6" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="G150" s="6" t="inlineStr">
+      <c r="G169" s="6" t="inlineStr">
         <is>
           <t>Business size (S=Small, O=Other)</t>
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="5" t="inlineStr">
+    <row r="170">
+      <c r="A170" s="5" t="inlineStr">
         <is>
           <t>security_clearance</t>
         </is>
       </c>
-      <c r="B151" s="5" t="inlineStr">
+      <c r="B170" s="5" t="inlineStr">
         <is>
           <t>VARCHAR(50)</t>
         </is>
       </c>
-      <c r="C151" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D151" s="5" t="inlineStr"/>
-      <c r="E151" s="5" t="inlineStr"/>
-      <c r="F151" s="5" t="inlineStr"/>
-      <c r="G151" s="5" t="inlineStr">
+      <c r="C170" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D170" s="5" t="inlineStr"/>
+      <c r="E170" s="5" t="inlineStr"/>
+      <c r="F170" s="5" t="inlineStr"/>
+      <c r="G170" s="5" t="inlineStr">
         <is>
           <t>Required clearance level</t>
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="6" t="inlineStr">
+    <row r="171">
+      <c r="A171" s="6" t="inlineStr">
         <is>
           <t>worksite</t>
         </is>
       </c>
-      <c r="B152" s="6" t="inlineStr">
+      <c r="B171" s="6" t="inlineStr">
         <is>
           <t>VARCHAR(100)</t>
         </is>
       </c>
-      <c r="C152" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D152" s="6" t="inlineStr"/>
-      <c r="E152" s="6" t="inlineStr"/>
-      <c r="F152" s="6" t="inlineStr"/>
-      <c r="G152" s="6" t="inlineStr">
+      <c r="C171" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D171" s="6" t="inlineStr"/>
+      <c r="E171" s="6" t="inlineStr"/>
+      <c r="F171" s="6" t="inlineStr"/>
+      <c r="G171" s="6" t="inlineStr">
         <is>
           <t>Work location requirements</t>
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="5" t="inlineStr">
+    <row r="172">
+      <c r="A172" s="5" t="inlineStr">
         <is>
           <t>contract_start</t>
         </is>
       </c>
-      <c r="B153" s="5" t="inlineStr">
+      <c r="B172" s="5" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="C153" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D153" s="5" t="inlineStr"/>
-      <c r="E153" s="5" t="inlineStr"/>
-      <c r="F153" s="5" t="inlineStr"/>
-      <c r="G153" s="5" t="inlineStr"/>
-    </row>
-    <row r="154">
-      <c r="A154" s="6" t="inlineStr">
+      <c r="C172" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D172" s="5" t="inlineStr"/>
+      <c r="E172" s="5" t="inlineStr"/>
+      <c r="F172" s="5" t="inlineStr"/>
+      <c r="G172" s="5" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="6" t="inlineStr">
         <is>
           <t>contract_end</t>
         </is>
       </c>
-      <c r="B154" s="6" t="inlineStr">
+      <c r="B173" s="6" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="C154" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D154" s="6" t="inlineStr"/>
-      <c r="E154" s="6" t="inlineStr"/>
-      <c r="F154" s="6" t="inlineStr"/>
-      <c r="G154" s="6" t="inlineStr"/>
-    </row>
-    <row r="155">
-      <c r="A155" s="5" t="inlineStr">
+      <c r="C173" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D173" s="6" t="inlineStr"/>
+      <c r="E173" s="6" t="inlineStr"/>
+      <c r="F173" s="6" t="inlineStr"/>
+      <c r="G173" s="6" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="5" t="inlineStr">
         <is>
           <t>idv_piid</t>
         </is>
       </c>
-      <c r="B155" s="5" t="inlineStr">
+      <c r="B174" s="5" t="inlineStr">
         <is>
           <t>VARCHAR(50)</t>
         </is>
       </c>
-      <c r="C155" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D155" s="5" t="inlineStr"/>
-      <c r="E155" s="5" t="inlineStr"/>
-      <c r="F155" s="5" t="inlineStr"/>
-      <c r="G155" s="5" t="inlineStr">
+      <c r="C174" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D174" s="5" t="inlineStr"/>
+      <c r="E174" s="5" t="inlineStr"/>
+      <c r="F174" s="5" t="inlineStr"/>
+      <c r="G174" s="5" t="inlineStr">
         <is>
           <t>Indefinite Delivery Vehicle PIID</t>
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="6" t="inlineStr">
+    <row r="175">
+      <c r="A175" s="6" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="B156" s="6" t="inlineStr">
+      <c r="B175" s="6" t="inlineStr">
         <is>
           <t>VARCHAR(200)</t>
         </is>
       </c>
-      <c r="C156" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D156" s="6" t="inlineStr"/>
-      <c r="E156" s="6" t="inlineStr"/>
-      <c r="F156" s="6" t="inlineStr"/>
-      <c r="G156" s="6" t="inlineStr">
+      <c r="C175" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D175" s="6" t="inlineStr"/>
+      <c r="E175" s="6" t="inlineStr"/>
+      <c r="F175" s="6" t="inlineStr"/>
+      <c r="G175" s="6" t="inlineStr">
         <is>
           <t>Business type category</t>
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="5" t="inlineStr">
+    <row r="176">
+      <c r="A176" s="5" t="inlineStr">
         <is>
           <t>subcategory</t>
         </is>
       </c>
-      <c r="B157" s="5" t="inlineStr">
+      <c r="B176" s="5" t="inlineStr">
         <is>
           <t>VARCHAR(500)</t>
         </is>
       </c>
-      <c r="C157" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D157" s="5" t="inlineStr"/>
-      <c r="E157" s="5" t="inlineStr"/>
-      <c r="F157" s="5" t="inlineStr"/>
-      <c r="G157" s="5" t="inlineStr"/>
-    </row>
-    <row r="158">
-      <c r="A158" s="6" t="inlineStr">
+      <c r="C176" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D176" s="5" t="inlineStr"/>
+      <c r="E176" s="5" t="inlineStr"/>
+      <c r="F176" s="5" t="inlineStr"/>
+      <c r="G176" s="5" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="6" t="inlineStr">
         <is>
           <t>first_loaded_at</t>
         </is>
       </c>
-      <c r="B158" s="6" t="inlineStr">
+      <c r="B177" s="6" t="inlineStr">
         <is>
           <t>DATETIME</t>
         </is>
       </c>
-      <c r="C158" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D158" s="6" t="inlineStr">
+      <c r="C177" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D177" s="6" t="inlineStr">
         <is>
           <t>CURRENT_TIMESTAMP</t>
         </is>
       </c>
-      <c r="E158" s="6" t="inlineStr"/>
-      <c r="F158" s="6" t="inlineStr"/>
-      <c r="G158" s="6" t="inlineStr">
+      <c r="E177" s="6" t="inlineStr"/>
+      <c r="F177" s="6" t="inlineStr"/>
+      <c r="G177" s="6" t="inlineStr">
         <is>
           <t>Timestamp of initial ETL load</t>
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="5" t="inlineStr">
+    <row r="178">
+      <c r="A178" s="5" t="inlineStr">
         <is>
           <t>last_loaded_at</t>
         </is>
       </c>
-      <c r="B159" s="5" t="inlineStr">
+      <c r="B178" s="5" t="inlineStr">
         <is>
           <t>DATETIME</t>
         </is>
       </c>
-      <c r="C159" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D159" s="5" t="inlineStr">
+      <c r="C178" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D178" s="5" t="inlineStr">
         <is>
           <t>CURRENT_TIMESTAMP</t>
         </is>
       </c>
-      <c r="E159" s="5" t="inlineStr"/>
-      <c r="F159" s="5" t="inlineStr"/>
-      <c r="G159" s="5" t="inlineStr">
+      <c r="E178" s="5" t="inlineStr"/>
+      <c r="F178" s="5" t="inlineStr"/>
+      <c r="G178" s="5" t="inlineStr">
         <is>
           <t>Timestamp of most recent ETL load</t>
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="6" t="inlineStr">
+    <row r="179">
+      <c r="A179" s="6" t="inlineStr">
         <is>
           <t>last_load_id</t>
         </is>
       </c>
-      <c r="B160" s="6" t="inlineStr">
+      <c r="B179" s="6" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="C160" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D160" s="6" t="inlineStr"/>
-      <c r="E160" s="6" t="inlineStr"/>
-      <c r="F160" s="6" t="inlineStr"/>
-      <c r="G160" s="6" t="inlineStr">
+      <c r="C179" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D179" s="6" t="inlineStr"/>
+      <c r="E179" s="6" t="inlineStr"/>
+      <c r="F179" s="6" t="inlineStr"/>
+      <c r="G179" s="6" t="inlineStr">
         <is>
           <t>FK to etl_load_log for traceability</t>
         </is>
       </c>
     </row>
-    <row r="161"/>
+    <row r="180"/>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A85:G85"/>
+  <mergeCells count="7">
+    <mergeCell ref="A66:G66"/>
+    <mergeCell ref="A118:G118"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A131:G131"/>
+    <mergeCell ref="A157:G157"/>
+    <mergeCell ref="A104:G104"/>
     <mergeCell ref="A47:G47"/>
-    <mergeCell ref="A112:G112"/>
-    <mergeCell ref="A138:G138"/>
-    <mergeCell ref="A99:G99"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14880,7 +13951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16721,11 +15792,370 @@
       </c>
     </row>
     <row r="73"/>
+    <row r="74">
+      <c r="A74" s="8" t="inlineStr">
+        <is>
+          <t>ai_usage_log</t>
+        </is>
+      </c>
+      <c r="B74" s="9" t="n"/>
+      <c r="C74" s="9" t="n"/>
+      <c r="D74" s="9" t="n"/>
+      <c r="E74" s="9" t="n"/>
+      <c r="F74" s="9" t="n"/>
+      <c r="G74" s="9" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="10" t="inlineStr">
+        <is>
+          <t>Column Name</t>
+        </is>
+      </c>
+      <c r="B75" s="10" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="C75" s="10" t="inlineStr">
+        <is>
+          <t>Nullable</t>
+        </is>
+      </c>
+      <c r="D75" s="10" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="E75" s="10" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="F75" s="10" t="inlineStr">
+        <is>
+          <t>Index</t>
+        </is>
+      </c>
+      <c r="G75" s="10" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>usage_id</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr"/>
+      <c r="E76" s="6" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G76" s="6" t="inlineStr">
+        <is>
+          <t>Auto-increment usage log identifier</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>notice_id</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>VARCHAR(100)</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr"/>
+      <c r="E77" s="5" t="inlineStr"/>
+      <c r="F77" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t>SAM.gov opportunity identifier</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>attachment_id</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr"/>
+      <c r="E78" s="6" t="inlineStr"/>
+      <c r="F78" s="6" t="inlineStr"/>
+      <c r="G78" s="6" t="inlineStr">
+        <is>
+          <t>Auto-increment attachment identifier</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>VARCHAR(50)</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr"/>
+      <c r="E79" s="5" t="inlineStr"/>
+      <c r="F79" s="5" t="inlineStr"/>
+      <c r="G79" s="5" t="inlineStr">
+        <is>
+          <t>AI model name (e.g. claude-3-haiku)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>input_tokens</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr"/>
+      <c r="E80" s="6" t="inlineStr"/>
+      <c r="F80" s="6" t="inlineStr"/>
+      <c r="G80" s="6" t="inlineStr">
+        <is>
+          <t>Number of input tokens consumed</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>output_tokens</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr"/>
+      <c r="E81" s="5" t="inlineStr"/>
+      <c r="F81" s="5" t="inlineStr"/>
+      <c r="G81" s="5" t="inlineStr">
+        <is>
+          <t>Number of output tokens generated</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>cache_read_tokens</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E82" s="6" t="inlineStr"/>
+      <c r="F82" s="6" t="inlineStr"/>
+      <c r="G82" s="6" t="inlineStr">
+        <is>
+          <t>Tokens read from prompt cache</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>cache_write_tokens</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="inlineStr"/>
+      <c r="F83" s="5" t="inlineStr"/>
+      <c r="G83" s="5" t="inlineStr">
+        <is>
+          <t>Tokens written to prompt cache</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>cost_usd</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>DECIMAL(10</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="inlineStr"/>
+      <c r="E84" s="6" t="inlineStr"/>
+      <c r="F84" s="6" t="inlineStr"/>
+      <c r="G84" s="6" t="inlineStr">
+        <is>
+          <t>Estimated cost in USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>requested_by</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="inlineStr"/>
+      <c r="E85" s="5" t="inlineStr"/>
+      <c r="F85" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G85" s="5" t="inlineStr">
+        <is>
+          <t>User who made the request</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>DATETIME</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="E86" s="6" t="inlineStr"/>
+      <c r="F86" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G86" s="6" t="inlineStr">
+        <is>
+          <t>Row creation timestamp</t>
+        </is>
+      </c>
+    </row>
+    <row r="87"/>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A40:G40"/>
     <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A74:G74"/>
     <mergeCell ref="A59:G59"/>
     <mergeCell ref="A49:G49"/>
     <mergeCell ref="A28:G28"/>
